--- a/signal_coodination/experiment.xlsx
+++ b/signal_coodination/experiment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50a7229fe28fb870/デスクトップ/randy_utokyo/signal_coodination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A802CD8D-A193-4DA2-9C7F-D0478ED86862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="14_{A802CD8D-A193-4DA2-9C7F-D0478ED86862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB525A4B-304A-4ABA-B367-6B72B6E4638F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="22410" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z157"/>
+  <dimension ref="A1:U157"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="15" max="15" width="12.25" style="1" customWidth="1"/>
@@ -496,7 +496,7 @@
     <col min="21" max="21" width="11.08203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>311</v>
       </c>
@@ -633,7 +633,7 @@
         <v>3.7037037037037051</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>311</v>
       </c>
@@ -705,7 +705,7 @@
         <v>3.8986354775828462</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>311</v>
       </c>
@@ -777,7 +777,7 @@
         <v>4.1152263374485587</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>311</v>
       </c>
@@ -849,7 +849,7 @@
         <v>4.3572984749455328</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>311</v>
       </c>
@@ -921,7 +921,7 @@
         <v>4.6296296296296289</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>311</v>
       </c>
@@ -992,11 +992,8 @@
         <f t="shared" si="5"/>
         <v>4.9382716049382651</v>
       </c>
-      <c r="Z7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>311</v>
       </c>
@@ -1068,7 +1065,7 @@
         <v>5.2910052910052858</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>311</v>
       </c>
@@ -1140,7 +1137,7 @@
         <v>5.6980056980056917</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>311</v>
       </c>
@@ -1212,7 +1209,7 @@
         <v>6.1728395061728287</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>311</v>
       </c>
@@ -1284,7 +1281,7 @@
         <v>6.734006734006722</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>311</v>
       </c>
@@ -1356,7 +1353,7 @@
         <v>7.4074074074073932</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>311</v>
       </c>
@@ -1428,7 +1425,7 @@
         <v>8.2304526748970996</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>311</v>
       </c>
@@ -1500,7 +1497,7 @@
         <v>9.2592592592592364</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>312</v>
       </c>
@@ -1572,7 +1569,7 @@
         <v>4.6296296296296306</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>312</v>
       </c>

--- a/signal_coodination/experiment.xlsx
+++ b/signal_coodination/experiment.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50a7229fe28fb870/デスクトップ/randy_utokyo/signal_coodination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="14_{A802CD8D-A193-4DA2-9C7F-D0478ED86862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB525A4B-304A-4ABA-B367-6B72B6E4638F}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="14_{A802CD8D-A193-4DA2-9C7F-D0478ED86862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D5C2518-0067-4F44-A800-8003B7DD8472}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="22410" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$157</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -484,7 +487,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U157"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:V157"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="15" max="15" width="12.25" style="1" customWidth="1"/>
@@ -496,7 +500,7 @@
     <col min="21" max="21" width="11.08203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>311</v>
       </c>
@@ -569,33 +573,33 @@
         <v>50</v>
       </c>
       <c r="C2">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E2">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F2">
         <f>SUM(C2:E2)</f>
-        <v>666.66666666666686</v>
+        <v>1333.3333333333337</v>
       </c>
       <c r="G2">
         <f t="shared" ref="G2:G33" si="0">C2/(120*$B2*1000/3600)</f>
-        <v>0.12500000000000011</v>
+        <v>0.25000000000000022</v>
       </c>
       <c r="H2">
         <f t="shared" ref="H2:H33" si="1">D2/(120*$B2*1000/3600)</f>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I33" si="2">E2/(120*$B2*1000/3600)</f>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="J2">
         <f t="shared" ref="J2:J33" si="3">SUM(G2:I2)</f>
-        <v>0.40000000000000013</v>
+        <v>0.80000000000000027</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -626,14 +630,14 @@
       </c>
       <c r="T2">
         <f t="shared" ref="T2:T33" si="4">F2/B2*1000/3600</f>
-        <v>3.7037037037037051</v>
+        <v>7.4074074074074101</v>
       </c>
       <c r="U2">
         <f t="shared" ref="U2:U33" si="5">S2+T2</f>
-        <v>3.7037037037037051</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>7.4074074074074101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>311</v>
       </c>
@@ -641,33 +645,33 @@
         <v>47.5</v>
       </c>
       <c r="C3">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D3">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E3">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F66" si="6">SUM(C3:E3)</f>
-        <v>666.66666666666674</v>
+        <v>1333.3333333333335</v>
       </c>
       <c r="G3">
         <f t="shared" si="0"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>0.15789473684210528</v>
+        <v>0.31578947368421056</v>
       </c>
       <c r="I3">
         <f t="shared" si="2"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="J3">
         <f t="shared" si="3"/>
-        <v>0.4210526315789474</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -698,14 +702,14 @@
       </c>
       <c r="T3">
         <f t="shared" si="4"/>
-        <v>3.8986354775828462</v>
+        <v>7.7972709551656925</v>
       </c>
       <c r="U3">
         <f t="shared" si="5"/>
-        <v>3.8986354775828462</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>7.7972709551656925</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>311</v>
       </c>
@@ -713,33 +717,33 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>208.333333333333</v>
+        <v>416.666666666666</v>
       </c>
       <c r="D4">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E4">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F4">
         <f t="shared" si="6"/>
-        <v>666.66666666666652</v>
+        <v>1333.333333333333</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>0.13888888888888867</v>
+        <v>0.27777777777777735</v>
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
-        <v>0.13888888888888901</v>
+        <v>0.27777777777777801</v>
       </c>
       <c r="J4">
         <f t="shared" si="3"/>
-        <v>0.44444444444444436</v>
+        <v>0.88888888888888873</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -770,14 +774,14 @@
       </c>
       <c r="T4">
         <f t="shared" si="4"/>
-        <v>4.1152263374485587</v>
+        <v>8.2304526748971174</v>
       </c>
       <c r="U4">
         <f t="shared" si="5"/>
-        <v>4.1152263374485587</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>8.2304526748971174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>311</v>
       </c>
@@ -785,33 +789,33 @@
         <v>42.5</v>
       </c>
       <c r="C5">
-        <v>208.333333333333</v>
+        <v>416.666666666666</v>
       </c>
       <c r="D5">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E5">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F5">
         <f t="shared" si="6"/>
-        <v>666.66666666666652</v>
+        <v>1333.333333333333</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>0.14705882352941152</v>
+        <v>0.29411764705882304</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>0.1764705882352941</v>
+        <v>0.3529411764705882</v>
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>0.14705882352941188</v>
+        <v>0.29411764705882376</v>
       </c>
       <c r="J5">
         <f t="shared" si="3"/>
-        <v>0.47058823529411753</v>
+        <v>0.94117647058823506</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -842,14 +846,17 @@
       </c>
       <c r="T5">
         <f t="shared" si="4"/>
-        <v>4.3572984749455328</v>
+        <v>8.7145969498910656</v>
       </c>
       <c r="U5">
         <f t="shared" si="5"/>
-        <v>4.3572984749455328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>8.7145969498910656</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>311</v>
       </c>
@@ -857,33 +864,33 @@
         <v>40</v>
       </c>
       <c r="C6">
-        <v>208.333333333333</v>
+        <v>416.666666666666</v>
       </c>
       <c r="D6">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E6">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F6">
         <f t="shared" si="6"/>
-        <v>666.66666666666652</v>
+        <v>1333.333333333333</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0.15624999999999975</v>
+        <v>0.3124999999999995</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>0.1875</v>
+        <v>0.375</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
-        <v>0.15625000000000014</v>
+        <v>0.31250000000000028</v>
       </c>
       <c r="J6">
         <f t="shared" si="3"/>
-        <v>0.49999999999999989</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -914,14 +921,14 @@
       </c>
       <c r="T6">
         <f t="shared" si="4"/>
-        <v>4.6296296296296289</v>
+        <v>9.2592592592592577</v>
       </c>
       <c r="U6">
         <f t="shared" si="5"/>
-        <v>4.6296296296296289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.2592592592592577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>311</v>
       </c>
@@ -929,33 +936,33 @@
         <v>37.5</v>
       </c>
       <c r="C7">
-        <v>208.33333333333249</v>
+        <v>416.66666666666498</v>
       </c>
       <c r="D7">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E7">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F7">
         <f t="shared" si="6"/>
-        <v>666.66666666666595</v>
+        <v>1333.3333333333319</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.16666666666666599</v>
+        <v>0.33333333333333198</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>0.16666666666666682</v>
+        <v>0.33333333333333365</v>
       </c>
       <c r="J7">
         <f t="shared" si="3"/>
-        <v>0.53333333333333288</v>
+        <v>1.0666666666666658</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -986,14 +993,14 @@
       </c>
       <c r="T7">
         <f t="shared" si="4"/>
-        <v>4.9382716049382651</v>
+        <v>9.8765432098765302</v>
       </c>
       <c r="U7">
         <f t="shared" si="5"/>
-        <v>4.9382716049382651</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.8765432098765302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>311</v>
       </c>
@@ -1001,33 +1008,33 @@
         <v>35</v>
       </c>
       <c r="C8">
-        <v>208.33333333333249</v>
+        <v>416.66666666666498</v>
       </c>
       <c r="D8">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E8">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F8">
         <f t="shared" si="6"/>
-        <v>666.66666666666595</v>
+        <v>1333.3333333333319</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>0.17857142857142783</v>
+        <v>0.35714285714285565</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>0.21428571428571427</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>0.17857142857142871</v>
+        <v>0.35714285714285743</v>
       </c>
       <c r="J8">
         <f t="shared" si="3"/>
-        <v>0.57142857142857084</v>
+        <v>1.1428571428571417</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1058,14 +1065,14 @@
       </c>
       <c r="T8">
         <f t="shared" si="4"/>
-        <v>5.2910052910052858</v>
+        <v>10.582010582010572</v>
       </c>
       <c r="U8">
         <f t="shared" si="5"/>
-        <v>5.2910052910052858</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.582010582010572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>311</v>
       </c>
@@ -1073,33 +1080,33 @@
         <v>32.5</v>
       </c>
       <c r="C9">
-        <v>208.33333333333249</v>
+        <v>416.66666666666498</v>
       </c>
       <c r="D9">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E9">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F9">
         <f t="shared" si="6"/>
-        <v>666.66666666666595</v>
+        <v>1333.3333333333319</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>0.19230769230769154</v>
+        <v>0.38461538461538308</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>0.23076923076923078</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>0.19230769230769248</v>
+        <v>0.38461538461538497</v>
       </c>
       <c r="J9">
         <f t="shared" si="3"/>
-        <v>0.61538461538461486</v>
+        <v>1.2307692307692297</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1130,14 +1137,14 @@
       </c>
       <c r="T9">
         <f t="shared" si="4"/>
-        <v>5.6980056980056917</v>
+        <v>11.396011396011383</v>
       </c>
       <c r="U9">
         <f t="shared" si="5"/>
-        <v>5.6980056980056917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.396011396011383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>311</v>
       </c>
@@ -1145,33 +1152,33 @@
         <v>30</v>
       </c>
       <c r="C10">
-        <v>208.33333333333201</v>
+        <v>416.66666666666401</v>
       </c>
       <c r="D10">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E10">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F10">
         <f t="shared" si="6"/>
-        <v>666.66666666666549</v>
+        <v>1333.333333333331</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>0.20833333333333201</v>
+        <v>0.41666666666666402</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>0.20833333333333351</v>
+        <v>0.41666666666666702</v>
       </c>
       <c r="J10">
         <f t="shared" si="3"/>
-        <v>0.66666666666666552</v>
+        <v>1.333333333333331</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1202,14 +1209,14 @@
       </c>
       <c r="T10">
         <f t="shared" si="4"/>
-        <v>6.1728395061728287</v>
+        <v>12.345679012345657</v>
       </c>
       <c r="U10">
         <f t="shared" si="5"/>
-        <v>6.1728395061728287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.345679012345657</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>311</v>
       </c>
@@ -1217,33 +1224,33 @@
         <v>27.5</v>
       </c>
       <c r="C11">
-        <v>208.33333333333201</v>
+        <v>416.66666666666401</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E11">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F11">
         <f t="shared" si="6"/>
-        <v>666.66666666666549</v>
+        <v>1333.333333333331</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>0.22727272727272582</v>
+        <v>0.45454545454545164</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>0.27272727272727276</v>
+        <v>0.54545454545454553</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>0.22727272727272749</v>
+        <v>0.45454545454545497</v>
       </c>
       <c r="J11">
         <f t="shared" si="3"/>
-        <v>0.72727272727272607</v>
+        <v>1.4545454545454521</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1274,14 +1281,14 @@
       </c>
       <c r="T11">
         <f t="shared" si="4"/>
-        <v>6.734006734006722</v>
+        <v>13.468013468013444</v>
       </c>
       <c r="U11">
         <f t="shared" si="5"/>
-        <v>6.734006734006722</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.468013468013444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>311</v>
       </c>
@@ -1289,33 +1296,33 @@
         <v>25</v>
       </c>
       <c r="C12">
-        <v>208.33333333333201</v>
+        <v>416.66666666666401</v>
       </c>
       <c r="D12">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E12">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F12">
         <f t="shared" si="6"/>
-        <v>666.66666666666549</v>
+        <v>1333.333333333331</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>0.24999999999999839</v>
+        <v>0.49999999999999678</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
-        <v>0.25000000000000022</v>
+        <v>0.50000000000000044</v>
       </c>
       <c r="J12">
         <f t="shared" si="3"/>
-        <v>0.7999999999999986</v>
+        <v>1.5999999999999972</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1346,14 +1353,14 @@
       </c>
       <c r="T12">
         <f t="shared" si="4"/>
-        <v>7.4074074074073932</v>
+        <v>14.814814814814786</v>
       </c>
       <c r="U12">
         <f t="shared" si="5"/>
-        <v>7.4074074074073932</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.814814814814786</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>311</v>
       </c>
@@ -1361,33 +1368,33 @@
         <v>22.5</v>
       </c>
       <c r="C13">
-        <v>208.3333333333315</v>
+        <v>416.66666666666299</v>
       </c>
       <c r="D13">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E13">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F13">
         <f t="shared" si="6"/>
-        <v>666.66666666666504</v>
+        <v>1333.3333333333301</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>0.27777777777777535</v>
+        <v>0.5555555555555507</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>0.27777777777777801</v>
+        <v>0.55555555555555602</v>
       </c>
       <c r="J13">
         <f t="shared" si="3"/>
-        <v>0.88888888888888673</v>
+        <v>1.7777777777777735</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1418,14 +1425,14 @@
       </c>
       <c r="T13">
         <f t="shared" si="4"/>
-        <v>8.2304526748970996</v>
+        <v>16.460905349794199</v>
       </c>
       <c r="U13">
         <f t="shared" si="5"/>
-        <v>8.2304526748970996</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>16.460905349794199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>311</v>
       </c>
@@ -1433,33 +1440,33 @@
         <v>20</v>
       </c>
       <c r="C14">
-        <v>208.3333333333315</v>
+        <v>416.66666666666299</v>
       </c>
       <c r="D14">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E14">
-        <v>208.33333333333351</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="F14">
         <f t="shared" si="6"/>
-        <v>666.66666666666504</v>
+        <v>1333.3333333333301</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>0.31249999999999728</v>
+        <v>0.62499999999999456</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>0.31250000000000028</v>
+        <v>0.62500000000000056</v>
       </c>
       <c r="J14">
         <f t="shared" si="3"/>
-        <v>0.99999999999999756</v>
+        <v>1.9999999999999951</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1490,14 +1497,14 @@
       </c>
       <c r="T14">
         <f t="shared" si="4"/>
-        <v>9.2592592592592364</v>
+        <v>18.518518518518473</v>
       </c>
       <c r="U14">
         <f t="shared" si="5"/>
-        <v>9.2592592592592364</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>18.518518518518473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>312</v>
       </c>
@@ -1505,33 +1512,33 @@
         <v>50</v>
       </c>
       <c r="C15">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D15">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E15">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F15">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>0.17500000000000002</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>0.17500000000000002</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="J15">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1562,14 +1569,14 @@
       </c>
       <c r="T15">
         <f t="shared" si="4"/>
-        <v>4.6296296296296306</v>
+        <v>9.2592592592592613</v>
       </c>
       <c r="U15">
         <f t="shared" si="5"/>
-        <v>4.6296296296296306</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.2592592592592613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>312</v>
       </c>
@@ -1577,33 +1584,33 @@
         <v>47.5</v>
       </c>
       <c r="C16">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D16">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E16">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F16">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>0.18421052631578949</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>0.15789473684210528</v>
+        <v>0.31578947368421056</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
-        <v>0.18421052631578949</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="J16">
         <f t="shared" si="3"/>
-        <v>0.52631578947368429</v>
+        <v>1.0526315789473686</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1634,14 +1641,14 @@
       </c>
       <c r="T16">
         <f t="shared" si="4"/>
-        <v>4.8732943469785592</v>
+        <v>9.7465886939571185</v>
       </c>
       <c r="U16">
         <f t="shared" si="5"/>
-        <v>4.8732943469785592</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.7465886939571185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>312</v>
       </c>
@@ -1649,33 +1656,33 @@
         <v>45</v>
       </c>
       <c r="C17">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D17">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E17">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F17">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>0.19444444444444445</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
-        <v>0.19444444444444445</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J17">
         <f t="shared" si="3"/>
-        <v>0.55555555555555558</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1706,14 +1713,14 @@
       </c>
       <c r="T17">
         <f t="shared" si="4"/>
-        <v>5.1440329218107008</v>
+        <v>10.288065843621402</v>
       </c>
       <c r="U17">
         <f t="shared" si="5"/>
-        <v>5.1440329218107008</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.288065843621402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>312</v>
       </c>
@@ -1721,33 +1728,33 @@
         <v>42.5</v>
       </c>
       <c r="C18">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D18">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E18">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F18">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>0.20588235294117646</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>0.1764705882352941</v>
+        <v>0.3529411764705882</v>
       </c>
       <c r="I18">
         <f t="shared" si="2"/>
-        <v>0.20588235294117646</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="J18">
         <f t="shared" si="3"/>
-        <v>0.58823529411764697</v>
+        <v>1.1764705882352939</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1778,14 +1785,14 @@
       </c>
       <c r="T18">
         <f t="shared" si="4"/>
-        <v>5.446623093681918</v>
+        <v>10.893246187363836</v>
       </c>
       <c r="U18">
         <f t="shared" si="5"/>
-        <v>5.446623093681918</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.893246187363836</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>312</v>
       </c>
@@ -1793,33 +1800,33 @@
         <v>40</v>
       </c>
       <c r="C19">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D19">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E19">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F19">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>0.21875000000000003</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>0.1875</v>
+        <v>0.375</v>
       </c>
       <c r="I19">
         <f t="shared" si="2"/>
-        <v>0.21875000000000003</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="J19">
         <f t="shared" si="3"/>
-        <v>0.625</v>
+        <v>1.25</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1850,14 +1857,14 @@
       </c>
       <c r="T19">
         <f t="shared" si="4"/>
-        <v>5.7870370370370381</v>
+        <v>11.574074074074076</v>
       </c>
       <c r="U19">
         <f t="shared" si="5"/>
-        <v>5.7870370370370381</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.574074074074076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>312</v>
       </c>
@@ -1865,33 +1872,33 @@
         <v>37.5</v>
       </c>
       <c r="C20">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D20">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E20">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F20">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>0.23333333333333334</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I20">
         <f t="shared" si="2"/>
-        <v>0.23333333333333334</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="J20">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1922,14 +1929,14 @@
       </c>
       <c r="T20">
         <f t="shared" si="4"/>
-        <v>6.1728395061728403</v>
+        <v>12.345679012345681</v>
       </c>
       <c r="U20">
         <f t="shared" si="5"/>
-        <v>6.1728395061728403</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.345679012345681</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>312</v>
       </c>
@@ -1937,33 +1944,33 @@
         <v>35</v>
       </c>
       <c r="C21">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D21">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E21">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F21">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H21">
         <f t="shared" si="1"/>
-        <v>0.21428571428571427</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I21">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J21">
         <f t="shared" si="3"/>
-        <v>0.7142857142857143</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1994,14 +2001,14 @@
       </c>
       <c r="T21">
         <f t="shared" si="4"/>
-        <v>6.6137566137566148</v>
+        <v>13.22751322751323</v>
       </c>
       <c r="U21">
         <f t="shared" si="5"/>
-        <v>6.6137566137566148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.22751322751323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>312</v>
       </c>
@@ -2009,33 +2016,33 @@
         <v>32.5</v>
       </c>
       <c r="C22">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D22">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E22">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F22">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>0.26923076923076927</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>0.23076923076923078</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="I22">
         <f t="shared" si="2"/>
-        <v>0.26923076923076927</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="J22">
         <f t="shared" si="3"/>
-        <v>0.76923076923076927</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2066,14 +2073,14 @@
       </c>
       <c r="T22">
         <f t="shared" si="4"/>
-        <v>7.1225071225071233</v>
+        <v>14.245014245014247</v>
       </c>
       <c r="U22">
         <f t="shared" si="5"/>
-        <v>7.1225071225071233</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.245014245014247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>312</v>
       </c>
@@ -2081,33 +2088,33 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D23">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E23">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F23">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
-        <v>0.29166666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H23">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I23">
         <f t="shared" si="2"/>
-        <v>0.29166666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J23">
         <f t="shared" si="3"/>
-        <v>0.83333333333333348</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2138,14 +2145,14 @@
       </c>
       <c r="T23">
         <f t="shared" si="4"/>
-        <v>7.7160493827160499</v>
+        <v>15.4320987654321</v>
       </c>
       <c r="U23">
         <f t="shared" si="5"/>
-        <v>7.7160493827160499</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.4320987654321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>312</v>
       </c>
@@ -2153,33 +2160,33 @@
         <v>27.5</v>
       </c>
       <c r="C24">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D24">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E24">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F24">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G24">
         <f t="shared" si="0"/>
-        <v>0.31818181818181823</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>0.27272727272727276</v>
+        <v>0.54545454545454553</v>
       </c>
       <c r="I24">
         <f t="shared" si="2"/>
-        <v>0.31818181818181823</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="J24">
         <f t="shared" si="3"/>
-        <v>0.90909090909090928</v>
+        <v>1.8181818181818186</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2210,14 +2217,14 @@
       </c>
       <c r="T24">
         <f t="shared" si="4"/>
-        <v>8.4175084175084187</v>
+        <v>16.835016835016837</v>
       </c>
       <c r="U24">
         <f t="shared" si="5"/>
-        <v>8.4175084175084187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>16.835016835016837</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>312</v>
       </c>
@@ -2225,33 +2232,33 @@
         <v>25</v>
       </c>
       <c r="C25">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D25">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E25">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F25">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>0.35000000000000003</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I25">
         <f t="shared" si="2"/>
-        <v>0.35000000000000003</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="J25">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -2282,14 +2289,14 @@
       </c>
       <c r="T25">
         <f t="shared" si="4"/>
-        <v>9.2592592592592613</v>
+        <v>18.518518518518523</v>
       </c>
       <c r="U25">
         <f t="shared" si="5"/>
-        <v>9.2592592592592613</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>18.518518518518523</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>312</v>
       </c>
@@ -2297,33 +2304,33 @@
         <v>22.5</v>
       </c>
       <c r="C26">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D26">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E26">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F26">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G26">
         <f t="shared" si="0"/>
-        <v>0.3888888888888889</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="H26">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I26">
         <f t="shared" si="2"/>
-        <v>0.3888888888888889</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="J26">
         <f t="shared" si="3"/>
-        <v>1.1111111111111112</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -2354,14 +2361,14 @@
       </c>
       <c r="T26">
         <f t="shared" si="4"/>
-        <v>10.288065843621402</v>
+        <v>20.576131687242803</v>
       </c>
       <c r="U26">
         <f t="shared" si="5"/>
-        <v>10.288065843621402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>20.576131687242803</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>312</v>
       </c>
@@ -2369,33 +2376,33 @@
         <v>20</v>
       </c>
       <c r="C27">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D27">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E27">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F27">
         <f t="shared" si="6"/>
-        <v>833.33333333333348</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G27">
         <f t="shared" si="0"/>
-        <v>0.43750000000000006</v>
+        <v>0.87500000000000011</v>
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="I27">
         <f t="shared" si="2"/>
-        <v>0.43750000000000006</v>
+        <v>0.87500000000000011</v>
       </c>
       <c r="J27">
         <f t="shared" si="3"/>
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2426,11 +2433,11 @@
       </c>
       <c r="T27">
         <f t="shared" si="4"/>
-        <v>11.574074074074076</v>
+        <v>23.148148148148152</v>
       </c>
       <c r="U27">
         <f t="shared" si="5"/>
-        <v>11.574074074074076</v>
+        <v>23.148148148148152</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2441,33 +2448,33 @@
         <v>50</v>
       </c>
       <c r="C28">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D28">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E28">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F28">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G28">
         <f t="shared" si="0"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H28">
         <f t="shared" si="1"/>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="I28">
         <f t="shared" si="2"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="J28">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -2498,11 +2505,11 @@
       </c>
       <c r="T28">
         <f t="shared" si="4"/>
-        <v>5.5555555555555554</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U28">
         <f t="shared" si="5"/>
-        <v>5.5555555555555554</v>
+        <v>11.111111111111111</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2513,33 +2520,33 @@
         <v>47.5</v>
       </c>
       <c r="C29">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D29">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E29">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F29">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G29">
         <f t="shared" si="0"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="H29">
         <f t="shared" si="1"/>
-        <v>0.15789473684210528</v>
+        <v>0.31578947368421056</v>
       </c>
       <c r="I29">
         <f t="shared" si="2"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="J29">
         <f t="shared" si="3"/>
-        <v>0.63157894736842102</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2570,11 +2577,11 @@
       </c>
       <c r="T29">
         <f t="shared" si="4"/>
-        <v>5.8479532163742691</v>
+        <v>11.695906432748538</v>
       </c>
       <c r="U29">
         <f t="shared" si="5"/>
-        <v>5.8479532163742691</v>
+        <v>11.695906432748538</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2585,33 +2592,33 @@
         <v>45</v>
       </c>
       <c r="C30">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D30">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E30">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F30">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G30">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I30">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J30">
         <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2642,11 +2649,11 @@
       </c>
       <c r="T30">
         <f t="shared" si="4"/>
-        <v>6.1728395061728394</v>
+        <v>12.345679012345679</v>
       </c>
       <c r="U30">
         <f t="shared" si="5"/>
-        <v>6.1728395061728394</v>
+        <v>12.345679012345679</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2657,33 +2664,33 @@
         <v>42.5</v>
       </c>
       <c r="C31">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D31">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E31">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F31">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G31">
         <f t="shared" si="0"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>0.1764705882352941</v>
+        <v>0.3529411764705882</v>
       </c>
       <c r="I31">
         <f t="shared" si="2"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J31">
         <f t="shared" si="3"/>
-        <v>0.70588235294117641</v>
+        <v>1.4117647058823528</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2714,11 +2721,11 @@
       </c>
       <c r="T31">
         <f t="shared" si="4"/>
-        <v>6.5359477124183014</v>
+        <v>13.071895424836603</v>
       </c>
       <c r="U31">
         <f t="shared" si="5"/>
-        <v>6.5359477124183014</v>
+        <v>13.071895424836603</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2729,33 +2736,33 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D32">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E32">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F32">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="H32">
         <f t="shared" si="1"/>
-        <v>0.1875</v>
+        <v>0.375</v>
       </c>
       <c r="I32">
         <f t="shared" si="2"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="J32">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2786,11 +2793,11 @@
       </c>
       <c r="T32">
         <f t="shared" si="4"/>
-        <v>6.9444444444444446</v>
+        <v>13.888888888888889</v>
       </c>
       <c r="U32">
         <f t="shared" si="5"/>
-        <v>6.9444444444444446</v>
+        <v>13.888888888888889</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2801,33 +2808,33 @@
         <v>37.5</v>
       </c>
       <c r="C33">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D33">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E33">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F33">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I33">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J33">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2858,11 +2865,11 @@
       </c>
       <c r="T33">
         <f t="shared" si="4"/>
-        <v>7.4074074074074074</v>
+        <v>14.814814814814815</v>
       </c>
       <c r="U33">
         <f t="shared" si="5"/>
-        <v>7.4074074074074074</v>
+        <v>14.814814814814815</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2873,33 +2880,33 @@
         <v>35</v>
       </c>
       <c r="C34">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D34">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E34">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F34">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G34">
         <f t="shared" ref="G34:G65" si="7">C34/(120*$B34*1000/3600)</f>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="H34">
         <f t="shared" ref="H34:H65" si="8">D34/(120*$B34*1000/3600)</f>
-        <v>0.21428571428571427</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I34">
         <f t="shared" ref="I34:I65" si="9">E34/(120*$B34*1000/3600)</f>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="J34">
         <f t="shared" ref="J34:J65" si="10">SUM(G34:I34)</f>
-        <v>0.8571428571428571</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2930,11 +2937,11 @@
       </c>
       <c r="T34">
         <f t="shared" ref="T34:T65" si="11">F34/B34*1000/3600</f>
-        <v>7.9365079365079367</v>
+        <v>15.873015873015873</v>
       </c>
       <c r="U34">
         <f t="shared" ref="U34:U65" si="12">S34+T34</f>
-        <v>7.9365079365079367</v>
+        <v>15.873015873015873</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2945,33 +2952,33 @@
         <v>32.5</v>
       </c>
       <c r="C35">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D35">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E35">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F35">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G35">
         <f t="shared" si="7"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="H35">
         <f t="shared" si="8"/>
-        <v>0.23076923076923078</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="I35">
         <f t="shared" si="9"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J35">
         <f t="shared" si="10"/>
-        <v>0.92307692307692313</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -3002,11 +3009,11 @@
       </c>
       <c r="T35">
         <f t="shared" si="11"/>
-        <v>8.5470085470085468</v>
+        <v>17.094017094017094</v>
       </c>
       <c r="U35">
         <f t="shared" si="12"/>
-        <v>8.5470085470085468</v>
+        <v>17.094017094017094</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3017,33 +3024,33 @@
         <v>30</v>
       </c>
       <c r="C36">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D36">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E36">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F36">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G36">
         <f t="shared" si="7"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="H36">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I36">
         <f t="shared" si="9"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="J36">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -3074,11 +3081,11 @@
       </c>
       <c r="T36">
         <f t="shared" si="11"/>
-        <v>9.2592592592592595</v>
+        <v>18.518518518518519</v>
       </c>
       <c r="U36">
         <f t="shared" si="12"/>
-        <v>9.2592592592592595</v>
+        <v>18.518518518518519</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3089,33 +3096,33 @@
         <v>27.5</v>
       </c>
       <c r="C37">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D37">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E37">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F37">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G37">
         <f t="shared" si="7"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="H37">
         <f t="shared" si="8"/>
-        <v>0.27272727272727276</v>
+        <v>0.54545454545454553</v>
       </c>
       <c r="I37">
         <f t="shared" si="9"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="J37">
         <f t="shared" si="10"/>
-        <v>1.0909090909090911</v>
+        <v>2.1818181818181821</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -3146,11 +3153,11 @@
       </c>
       <c r="T37">
         <f t="shared" si="11"/>
-        <v>10.101010101010102</v>
+        <v>20.202020202020204</v>
       </c>
       <c r="U37">
         <f t="shared" si="12"/>
-        <v>10.101010101010102</v>
+        <v>20.202020202020204</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3161,33 +3168,33 @@
         <v>25</v>
       </c>
       <c r="C38">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D38">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E38">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F38">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G38">
         <f t="shared" si="7"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H38">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I38">
         <f t="shared" si="9"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J38">
         <f t="shared" si="10"/>
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -3218,11 +3225,11 @@
       </c>
       <c r="T38">
         <f t="shared" si="11"/>
-        <v>11.111111111111111</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="U38">
         <f t="shared" si="12"/>
-        <v>11.111111111111111</v>
+        <v>22.222222222222221</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3233,33 +3240,33 @@
         <v>22.5</v>
       </c>
       <c r="C39">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D39">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E39">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F39">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G39">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I39">
         <f t="shared" si="9"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <f t="shared" si="10"/>
-        <v>1.3333333333333333</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -3290,11 +3297,11 @@
       </c>
       <c r="T39">
         <f t="shared" si="11"/>
-        <v>12.345679012345679</v>
+        <v>24.691358024691358</v>
       </c>
       <c r="U39">
         <f t="shared" si="12"/>
-        <v>12.345679012345679</v>
+        <v>24.691358024691358</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3305,33 +3312,33 @@
         <v>20</v>
       </c>
       <c r="C40">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D40">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E40">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F40">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G40">
         <f t="shared" si="7"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="H40">
         <f t="shared" si="8"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="I40">
         <f t="shared" si="9"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="J40">
         <f t="shared" si="10"/>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -3362,11 +3369,11 @@
       </c>
       <c r="T40">
         <f t="shared" si="11"/>
-        <v>13.888888888888889</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="U40">
         <f t="shared" si="12"/>
-        <v>13.888888888888889</v>
+        <v>27.777777777777779</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3377,33 +3384,33 @@
         <v>50</v>
       </c>
       <c r="C41">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D41">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E41">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F41">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G41">
         <f t="shared" si="7"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="H41">
         <f t="shared" si="8"/>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="I41">
         <f t="shared" si="9"/>
-        <v>0.125</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="J41">
         <f t="shared" si="10"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -3434,11 +3441,11 @@
       </c>
       <c r="T41">
         <f t="shared" si="11"/>
-        <v>3.7037037037037042</v>
+        <v>9.2592592592592595</v>
       </c>
       <c r="U41">
         <f t="shared" si="12"/>
-        <v>3.7037037037037042</v>
+        <v>9.2592592592592595</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3449,33 +3456,33 @@
         <v>47.5</v>
       </c>
       <c r="C42">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D42">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E42">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F42">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G42">
         <f t="shared" si="7"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="H42">
         <f t="shared" si="8"/>
-        <v>0.15789473684210528</v>
+        <v>0.31578947368421056</v>
       </c>
       <c r="I42">
         <f t="shared" si="9"/>
-        <v>0.13157894736842107</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="J42">
         <f t="shared" si="10"/>
-        <v>0.4210526315789474</v>
+        <v>1.0526315789473686</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -3506,11 +3513,11 @@
       </c>
       <c r="T42">
         <f t="shared" si="11"/>
-        <v>3.8986354775828462</v>
+        <v>9.7465886939571167</v>
       </c>
       <c r="U42">
         <f t="shared" si="12"/>
-        <v>3.8986354775828462</v>
+        <v>9.7465886939571167</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3521,33 +3528,33 @@
         <v>45</v>
       </c>
       <c r="C43">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D43">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E43">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F43">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G43">
         <f t="shared" si="7"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="H43">
         <f t="shared" si="8"/>
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I43">
         <f t="shared" si="9"/>
-        <v>0.1388888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="J43">
         <f t="shared" si="10"/>
-        <v>0.44444444444444448</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -3578,11 +3585,11 @@
       </c>
       <c r="T43">
         <f t="shared" si="11"/>
-        <v>4.1152263374485605</v>
+        <v>10.2880658436214</v>
       </c>
       <c r="U43">
         <f t="shared" si="12"/>
-        <v>4.1152263374485605</v>
+        <v>10.2880658436214</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3593,33 +3600,33 @@
         <v>42.5</v>
       </c>
       <c r="C44">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D44">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E44">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F44">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G44">
         <f t="shared" si="7"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="H44">
         <f t="shared" si="8"/>
-        <v>0.1764705882352941</v>
+        <v>0.3529411764705882</v>
       </c>
       <c r="I44">
         <f t="shared" si="9"/>
-        <v>0.14705882352941177</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J44">
         <f t="shared" si="10"/>
-        <v>0.47058823529411764</v>
+        <v>1.1764705882352939</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -3650,11 +3657,11 @@
       </c>
       <c r="T44">
         <f t="shared" si="11"/>
-        <v>4.3572984749455346</v>
+        <v>10.893246187363834</v>
       </c>
       <c r="U44">
         <f t="shared" si="12"/>
-        <v>4.3572984749455346</v>
+        <v>10.893246187363834</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3665,33 +3672,33 @@
         <v>40</v>
       </c>
       <c r="C45">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D45">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E45">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F45">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G45">
         <f t="shared" si="7"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="H45">
         <f t="shared" si="8"/>
-        <v>0.1875</v>
+        <v>0.375</v>
       </c>
       <c r="I45">
         <f t="shared" si="9"/>
-        <v>0.15625000000000003</v>
+        <v>0.5625</v>
       </c>
       <c r="J45">
         <f t="shared" si="10"/>
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3722,11 +3729,11 @@
       </c>
       <c r="T45">
         <f t="shared" si="11"/>
-        <v>4.6296296296296298</v>
+        <v>11.574074074074076</v>
       </c>
       <c r="U45">
         <f t="shared" si="12"/>
-        <v>4.6296296296296298</v>
+        <v>11.574074074074076</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3737,33 +3744,33 @@
         <v>37.5</v>
       </c>
       <c r="C46">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D46">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E46">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F46">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G46">
         <f t="shared" si="7"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="H46">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I46">
         <f t="shared" si="9"/>
-        <v>0.16666666666666669</v>
+        <v>0.6</v>
       </c>
       <c r="J46">
         <f t="shared" si="10"/>
-        <v>0.53333333333333344</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3794,11 +3801,11 @@
       </c>
       <c r="T46">
         <f t="shared" si="11"/>
-        <v>4.9382716049382713</v>
+        <v>12.345679012345681</v>
       </c>
       <c r="U46">
         <f t="shared" si="12"/>
-        <v>4.9382716049382713</v>
+        <v>12.345679012345681</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3809,33 +3816,33 @@
         <v>35</v>
       </c>
       <c r="C47">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D47">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E47">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F47">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G47">
         <f t="shared" si="7"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="H47">
         <f t="shared" si="8"/>
-        <v>0.21428571428571427</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>0.17857142857142858</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="J47">
         <f t="shared" si="10"/>
-        <v>0.5714285714285714</v>
+        <v>1.4285714285714284</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3866,11 +3873,11 @@
       </c>
       <c r="T47">
         <f t="shared" si="11"/>
-        <v>5.2910052910052912</v>
+        <v>13.227513227513228</v>
       </c>
       <c r="U47">
         <f t="shared" si="12"/>
-        <v>5.2910052910052912</v>
+        <v>13.227513227513228</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3881,33 +3888,33 @@
         <v>32.5</v>
       </c>
       <c r="C48">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D48">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E48">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F48">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G48">
         <f t="shared" si="7"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H48">
         <f t="shared" si="8"/>
-        <v>0.23076923076923078</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>0.19230769230769232</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J48">
         <f t="shared" si="10"/>
-        <v>0.61538461538461542</v>
+        <v>1.5384615384615388</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3938,11 +3945,11 @@
       </c>
       <c r="T48">
         <f t="shared" si="11"/>
-        <v>5.6980056980056988</v>
+        <v>14.245014245014245</v>
       </c>
       <c r="U48">
         <f t="shared" si="12"/>
-        <v>5.6980056980056988</v>
+        <v>14.245014245014245</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3953,33 +3960,33 @@
         <v>30</v>
       </c>
       <c r="C49">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D49">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E49">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F49">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G49">
         <f t="shared" si="7"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H49">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I49">
         <f t="shared" si="9"/>
-        <v>0.20833333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="J49">
         <f t="shared" si="10"/>
-        <v>0.66666666666666674</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -4010,11 +4017,11 @@
       </c>
       <c r="T49">
         <f t="shared" si="11"/>
-        <v>6.1728395061728403</v>
+        <v>15.432098765432098</v>
       </c>
       <c r="U49">
         <f t="shared" si="12"/>
-        <v>6.1728395061728403</v>
+        <v>15.432098765432098</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -4025,33 +4032,33 @@
         <v>27.5</v>
       </c>
       <c r="C50">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D50">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E50">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F50">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G50">
         <f t="shared" si="7"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="H50">
         <f t="shared" si="8"/>
-        <v>0.27272727272727276</v>
+        <v>0.54545454545454553</v>
       </c>
       <c r="I50">
         <f t="shared" si="9"/>
-        <v>0.22727272727272729</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="J50">
         <f t="shared" si="10"/>
-        <v>0.72727272727272729</v>
+        <v>1.8181818181818183</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -4082,11 +4089,11 @@
       </c>
       <c r="T50">
         <f t="shared" si="11"/>
-        <v>6.7340067340067353</v>
+        <v>16.835016835016834</v>
       </c>
       <c r="U50">
         <f t="shared" si="12"/>
-        <v>6.7340067340067353</v>
+        <v>16.835016835016834</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -4097,33 +4104,33 @@
         <v>25</v>
       </c>
       <c r="C51">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D51">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E51">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F51">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G51">
         <f t="shared" si="7"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H51">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I51">
         <f t="shared" si="9"/>
-        <v>0.25</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J51">
         <f t="shared" si="10"/>
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -4154,11 +4161,11 @@
       </c>
       <c r="T51">
         <f t="shared" si="11"/>
-        <v>7.4074074074074083</v>
+        <v>18.518518518518519</v>
       </c>
       <c r="U51">
         <f t="shared" si="12"/>
-        <v>7.4074074074074083</v>
+        <v>18.518518518518519</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -4169,33 +4176,33 @@
         <v>22.5</v>
       </c>
       <c r="C52">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D52">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E52">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F52">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G52">
         <f t="shared" si="7"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H52">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I52">
         <f t="shared" si="9"/>
-        <v>0.27777777777777779</v>
+        <v>1</v>
       </c>
       <c r="J52">
         <f t="shared" si="10"/>
-        <v>0.88888888888888895</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -4226,11 +4233,11 @@
       </c>
       <c r="T52">
         <f t="shared" si="11"/>
-        <v>8.230452674897121</v>
+        <v>20.5761316872428</v>
       </c>
       <c r="U52">
         <f t="shared" si="12"/>
-        <v>8.230452674897121</v>
+        <v>20.5761316872428</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -4241,33 +4248,33 @@
         <v>20</v>
       </c>
       <c r="C53">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D53">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E53">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F53">
         <f t="shared" si="6"/>
-        <v>666.66666666666674</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G53">
         <f t="shared" si="7"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="H53">
         <f t="shared" si="8"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="I53">
         <f t="shared" si="9"/>
-        <v>0.31250000000000006</v>
+        <v>1.125</v>
       </c>
       <c r="J53">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -4298,14 +4305,14 @@
       </c>
       <c r="T53">
         <f t="shared" si="11"/>
-        <v>9.2592592592592595</v>
+        <v>23.148148148148152</v>
       </c>
       <c r="U53">
         <f t="shared" si="12"/>
-        <v>9.2592592592592595</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>23.148148148148152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>321</v>
       </c>
@@ -4313,33 +4320,33 @@
         <v>50</v>
       </c>
       <c r="C54">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D54">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E54">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F54">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G54">
         <f t="shared" si="7"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="H54">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I54">
         <f t="shared" si="9"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="J54">
         <f t="shared" si="10"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -4370,14 +4377,14 @@
       </c>
       <c r="T54">
         <f t="shared" si="11"/>
-        <v>4.6296296296296298</v>
+        <v>9.2592592592592595</v>
       </c>
       <c r="U54">
         <f t="shared" si="12"/>
-        <v>4.6296296296296298</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.2592592592592595</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>321</v>
       </c>
@@ -4385,33 +4392,33 @@
         <v>47.5</v>
       </c>
       <c r="C55">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D55">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E55">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F55">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G55">
         <f t="shared" si="7"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="H55">
         <f t="shared" si="8"/>
-        <v>0.26315789473684215</v>
+        <v>0.52631578947368429</v>
       </c>
       <c r="I55">
         <f t="shared" si="9"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="J55">
         <f t="shared" si="10"/>
-        <v>0.52631578947368429</v>
+        <v>1.0526315789473686</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -4442,14 +4449,14 @@
       </c>
       <c r="T55">
         <f t="shared" si="11"/>
-        <v>4.8732943469785583</v>
+        <v>9.7465886939571167</v>
       </c>
       <c r="U55">
         <f t="shared" si="12"/>
-        <v>4.8732943469785583</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.7465886939571167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>321</v>
       </c>
@@ -4457,33 +4464,33 @@
         <v>45</v>
       </c>
       <c r="C56">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D56">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E56">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F56">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G56">
         <f t="shared" si="7"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="H56">
         <f t="shared" si="8"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I56">
         <f t="shared" si="9"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="J56">
         <f t="shared" si="10"/>
-        <v>0.55555555555555558</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -4514,14 +4521,14 @@
       </c>
       <c r="T56">
         <f t="shared" si="11"/>
-        <v>5.1440329218106999</v>
+        <v>10.2880658436214</v>
       </c>
       <c r="U56">
         <f t="shared" si="12"/>
-        <v>5.1440329218106999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.2880658436214</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>321</v>
       </c>
@@ -4529,33 +4536,33 @@
         <v>42.5</v>
       </c>
       <c r="C57">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D57">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E57">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F57">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G57">
         <f t="shared" si="7"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="H57">
         <f t="shared" si="8"/>
-        <v>0.29411764705882354</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="I57">
         <f t="shared" si="9"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="J57">
         <f t="shared" si="10"/>
-        <v>0.58823529411764708</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -4586,14 +4593,14 @@
       </c>
       <c r="T57">
         <f t="shared" si="11"/>
-        <v>5.4466230936819171</v>
+        <v>10.893246187363834</v>
       </c>
       <c r="U57">
         <f t="shared" si="12"/>
-        <v>5.4466230936819171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.893246187363834</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>321</v>
       </c>
@@ -4601,33 +4608,33 @@
         <v>40</v>
       </c>
       <c r="C58">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D58">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E58">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F58">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G58">
         <f t="shared" si="7"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="H58">
         <f t="shared" si="8"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I58">
         <f t="shared" si="9"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="J58">
         <f t="shared" si="10"/>
-        <v>0.62500000000000011</v>
+        <v>1.2500000000000002</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -4658,14 +4665,14 @@
       </c>
       <c r="T58">
         <f t="shared" si="11"/>
-        <v>5.7870370370370381</v>
+        <v>11.574074074074076</v>
       </c>
       <c r="U58">
         <f t="shared" si="12"/>
-        <v>5.7870370370370381</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.574074074074076</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>321</v>
       </c>
@@ -4673,33 +4680,33 @@
         <v>37.5</v>
       </c>
       <c r="C59">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D59">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E59">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F59">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G59">
         <f t="shared" si="7"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="H59">
         <f t="shared" si="8"/>
-        <v>0.33333333333333337</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I59">
         <f t="shared" si="9"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J59">
         <f t="shared" si="10"/>
-        <v>0.66666666666666674</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -4730,14 +4737,14 @@
       </c>
       <c r="T59">
         <f t="shared" si="11"/>
-        <v>6.1728395061728403</v>
+        <v>12.345679012345681</v>
       </c>
       <c r="U59">
         <f t="shared" si="12"/>
-        <v>6.1728395061728403</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.345679012345681</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>321</v>
       </c>
@@ -4745,33 +4752,33 @@
         <v>35</v>
       </c>
       <c r="C60">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D60">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E60">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F60">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G60">
         <f t="shared" si="7"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="H60">
         <f t="shared" si="8"/>
-        <v>0.35714285714285715</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I60">
         <f t="shared" si="9"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="J60">
         <f t="shared" si="10"/>
-        <v>0.7142857142857143</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -4802,14 +4809,14 @@
       </c>
       <c r="T60">
         <f t="shared" si="11"/>
-        <v>6.6137566137566139</v>
+        <v>13.227513227513228</v>
       </c>
       <c r="U60">
         <f t="shared" si="12"/>
-        <v>6.6137566137566139</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.227513227513228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>321</v>
       </c>
@@ -4817,33 +4824,33 @@
         <v>32.5</v>
       </c>
       <c r="C61">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D61">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E61">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F61">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G61">
         <f t="shared" si="7"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H61">
         <f t="shared" si="8"/>
-        <v>0.38461538461538464</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="I61">
         <f t="shared" si="9"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="J61">
         <f t="shared" si="10"/>
-        <v>0.76923076923076927</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -4874,14 +4881,14 @@
       </c>
       <c r="T61">
         <f t="shared" si="11"/>
-        <v>7.1225071225071224</v>
+        <v>14.245014245014245</v>
       </c>
       <c r="U61">
         <f t="shared" si="12"/>
-        <v>7.1225071225071224</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.245014245014245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>321</v>
       </c>
@@ -4889,33 +4896,33 @@
         <v>30</v>
       </c>
       <c r="C62">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D62">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E62">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F62">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G62">
         <f t="shared" si="7"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H62">
         <f t="shared" si="8"/>
-        <v>0.41666666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="I62">
         <f t="shared" si="9"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J62">
         <f t="shared" si="10"/>
-        <v>0.83333333333333337</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -4946,14 +4953,14 @@
       </c>
       <c r="T62">
         <f t="shared" si="11"/>
-        <v>7.716049382716049</v>
+        <v>15.432098765432098</v>
       </c>
       <c r="U62">
         <f t="shared" si="12"/>
-        <v>7.716049382716049</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.432098765432098</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>321</v>
       </c>
@@ -4961,33 +4968,33 @@
         <v>27.5</v>
       </c>
       <c r="C63">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D63">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E63">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F63">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G63">
         <f t="shared" si="7"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="H63">
         <f t="shared" si="8"/>
-        <v>0.45454545454545459</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="I63">
         <f t="shared" si="9"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="J63">
         <f t="shared" si="10"/>
-        <v>0.90909090909090917</v>
+        <v>1.8181818181818183</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -5018,14 +5025,14 @@
       </c>
       <c r="T63">
         <f t="shared" si="11"/>
-        <v>8.4175084175084169</v>
+        <v>16.835016835016834</v>
       </c>
       <c r="U63">
         <f t="shared" si="12"/>
-        <v>8.4175084175084169</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>16.835016835016834</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>321</v>
       </c>
@@ -5033,33 +5040,33 @@
         <v>25</v>
       </c>
       <c r="C64">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D64">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E64">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F64">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G64">
         <f t="shared" si="7"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H64">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <f t="shared" si="9"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J64">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -5090,14 +5097,14 @@
       </c>
       <c r="T64">
         <f t="shared" si="11"/>
-        <v>9.2592592592592595</v>
+        <v>18.518518518518519</v>
       </c>
       <c r="U64">
         <f t="shared" si="12"/>
-        <v>9.2592592592592595</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>18.518518518518519</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>321</v>
       </c>
@@ -5105,33 +5112,33 @@
         <v>22.5</v>
       </c>
       <c r="C65">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D65">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E65">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F65">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G65">
         <f t="shared" si="7"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H65">
         <f t="shared" si="8"/>
-        <v>0.55555555555555558</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="I65">
         <f t="shared" si="9"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="J65">
         <f t="shared" si="10"/>
-        <v>1.1111111111111112</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -5162,14 +5169,14 @@
       </c>
       <c r="T65">
         <f t="shared" si="11"/>
-        <v>10.2880658436214</v>
+        <v>20.5761316872428</v>
       </c>
       <c r="U65">
         <f t="shared" si="12"/>
-        <v>10.2880658436214</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>20.5761316872428</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>321</v>
       </c>
@@ -5177,33 +5184,33 @@
         <v>20</v>
       </c>
       <c r="C66">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D66">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E66">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F66">
         <f t="shared" si="6"/>
-        <v>833.33333333333337</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="G66">
         <f t="shared" ref="G66:G97" si="13">C66/(120*$B66*1000/3600)</f>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="H66">
         <f t="shared" ref="H66:H97" si="14">D66/(120*$B66*1000/3600)</f>
-        <v>0.62500000000000011</v>
+        <v>1.2500000000000002</v>
       </c>
       <c r="I66">
         <f t="shared" ref="I66:I97" si="15">E66/(120*$B66*1000/3600)</f>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="J66">
         <f t="shared" ref="J66:J97" si="16">SUM(G66:I66)</f>
-        <v>1.2500000000000002</v>
+        <v>2.5000000000000004</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -5234,14 +5241,14 @@
       </c>
       <c r="T66">
         <f t="shared" ref="T66:T97" si="17">F66/B66*1000/3600</f>
-        <v>11.574074074074076</v>
+        <v>23.148148148148152</v>
       </c>
       <c r="U66">
         <f t="shared" ref="U66:U97" si="18">S66+T66</f>
-        <v>11.574074074074076</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>23.148148148148152</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>322</v>
       </c>
@@ -5249,33 +5256,33 @@
         <v>50</v>
       </c>
       <c r="C67">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D67">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E67">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F67">
         <f t="shared" ref="F67:F130" si="19">SUM(C67:E67)</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G67">
         <f t="shared" si="13"/>
-        <v>0.17500000000000002</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="H67">
         <f t="shared" si="14"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I67">
         <f t="shared" si="15"/>
-        <v>0.17500000000000002</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="J67">
         <f t="shared" si="16"/>
-        <v>0.60000000000000009</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -5306,14 +5313,14 @@
       </c>
       <c r="T67">
         <f t="shared" si="17"/>
-        <v>5.5555555555555554</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U67">
         <f t="shared" si="18"/>
-        <v>5.5555555555555554</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.111111111111111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>322</v>
       </c>
@@ -5321,33 +5328,33 @@
         <v>47.5</v>
       </c>
       <c r="C68">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D68">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E68">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F68">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G68">
         <f t="shared" si="13"/>
-        <v>0.18421052631578949</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="H68">
         <f t="shared" si="14"/>
-        <v>0.26315789473684215</v>
+        <v>0.52631578947368429</v>
       </c>
       <c r="I68">
         <f t="shared" si="15"/>
-        <v>0.18421052631578949</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="J68">
         <f t="shared" si="16"/>
-        <v>0.63157894736842113</v>
+        <v>1.2631578947368423</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -5378,14 +5385,14 @@
       </c>
       <c r="T68">
         <f t="shared" si="17"/>
-        <v>5.8479532163742691</v>
+        <v>11.695906432748538</v>
       </c>
       <c r="U68">
         <f t="shared" si="18"/>
-        <v>5.8479532163742691</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.695906432748538</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>322</v>
       </c>
@@ -5393,33 +5400,33 @@
         <v>45</v>
       </c>
       <c r="C69">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D69">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E69">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F69">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G69">
         <f t="shared" si="13"/>
-        <v>0.19444444444444445</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="H69">
         <f t="shared" si="14"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I69">
         <f t="shared" si="15"/>
-        <v>0.19444444444444445</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J69">
         <f t="shared" si="16"/>
-        <v>0.66666666666666663</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -5450,14 +5457,14 @@
       </c>
       <c r="T69">
         <f t="shared" si="17"/>
-        <v>6.1728395061728394</v>
+        <v>12.345679012345679</v>
       </c>
       <c r="U69">
         <f t="shared" si="18"/>
-        <v>6.1728395061728394</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.345679012345679</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>322</v>
       </c>
@@ -5465,33 +5472,33 @@
         <v>42.5</v>
       </c>
       <c r="C70">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D70">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E70">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F70">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G70">
         <f t="shared" si="13"/>
-        <v>0.20588235294117646</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="H70">
         <f t="shared" si="14"/>
-        <v>0.29411764705882354</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="I70">
         <f t="shared" si="15"/>
-        <v>0.20588235294117646</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="J70">
         <f t="shared" si="16"/>
-        <v>0.70588235294117641</v>
+        <v>1.4117647058823528</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -5522,14 +5529,14 @@
       </c>
       <c r="T70">
         <f t="shared" si="17"/>
-        <v>6.5359477124183014</v>
+        <v>13.071895424836603</v>
       </c>
       <c r="U70">
         <f t="shared" si="18"/>
-        <v>6.5359477124183014</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.071895424836603</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>322</v>
       </c>
@@ -5537,33 +5544,33 @@
         <v>40</v>
       </c>
       <c r="C71">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D71">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E71">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F71">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G71">
         <f t="shared" si="13"/>
-        <v>0.21875000000000003</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="H71">
         <f t="shared" si="14"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I71">
         <f t="shared" si="15"/>
-        <v>0.21875000000000003</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="J71">
         <f t="shared" si="16"/>
-        <v>0.75000000000000011</v>
+        <v>1.5000000000000002</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -5594,14 +5601,14 @@
       </c>
       <c r="T71">
         <f t="shared" si="17"/>
-        <v>6.9444444444444446</v>
+        <v>13.888888888888889</v>
       </c>
       <c r="U71">
         <f t="shared" si="18"/>
-        <v>6.9444444444444446</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.888888888888889</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>322</v>
       </c>
@@ -5609,33 +5616,33 @@
         <v>37.5</v>
       </c>
       <c r="C72">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D72">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E72">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F72">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G72">
         <f t="shared" si="13"/>
-        <v>0.23333333333333334</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="H72">
         <f t="shared" si="14"/>
-        <v>0.33333333333333337</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I72">
         <f t="shared" si="15"/>
-        <v>0.23333333333333334</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="J72">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -5666,14 +5673,14 @@
       </c>
       <c r="T72">
         <f t="shared" si="17"/>
-        <v>7.4074074074074074</v>
+        <v>14.814814814814815</v>
       </c>
       <c r="U72">
         <f t="shared" si="18"/>
-        <v>7.4074074074074074</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.814814814814815</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>322</v>
       </c>
@@ -5681,33 +5688,33 @@
         <v>35</v>
       </c>
       <c r="C73">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D73">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E73">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F73">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G73">
         <f t="shared" si="13"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H73">
         <f t="shared" si="14"/>
-        <v>0.35714285714285715</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I73">
         <f t="shared" si="15"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J73">
         <f t="shared" si="16"/>
-        <v>0.85714285714285721</v>
+        <v>1.7142857142857144</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -5738,14 +5745,14 @@
       </c>
       <c r="T73">
         <f t="shared" si="17"/>
-        <v>7.9365079365079367</v>
+        <v>15.873015873015873</v>
       </c>
       <c r="U73">
         <f t="shared" si="18"/>
-        <v>7.9365079365079367</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.873015873015873</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>322</v>
       </c>
@@ -5753,33 +5760,33 @@
         <v>32.5</v>
       </c>
       <c r="C74">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D74">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E74">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F74">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G74">
         <f t="shared" si="13"/>
-        <v>0.26923076923076927</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="H74">
         <f t="shared" si="14"/>
-        <v>0.38461538461538464</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="I74">
         <f t="shared" si="15"/>
-        <v>0.26923076923076927</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="J74">
         <f t="shared" si="16"/>
-        <v>0.92307692307692324</v>
+        <v>1.8461538461538465</v>
       </c>
       <c r="K74">
         <v>0</v>
@@ -5810,14 +5817,14 @@
       </c>
       <c r="T74">
         <f t="shared" si="17"/>
-        <v>8.5470085470085468</v>
+        <v>17.094017094017094</v>
       </c>
       <c r="U74">
         <f t="shared" si="18"/>
-        <v>8.5470085470085468</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>17.094017094017094</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>322</v>
       </c>
@@ -5825,33 +5832,33 @@
         <v>30</v>
       </c>
       <c r="C75">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D75">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E75">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F75">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G75">
         <f t="shared" si="13"/>
-        <v>0.29166666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H75">
         <f t="shared" si="14"/>
-        <v>0.41666666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="I75">
         <f t="shared" si="15"/>
-        <v>0.29166666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J75">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -5882,14 +5889,14 @@
       </c>
       <c r="T75">
         <f t="shared" si="17"/>
-        <v>9.2592592592592595</v>
+        <v>18.518518518518519</v>
       </c>
       <c r="U75">
         <f t="shared" si="18"/>
-        <v>9.2592592592592595</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>18.518518518518519</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>322</v>
       </c>
@@ -5897,33 +5904,33 @@
         <v>27.5</v>
       </c>
       <c r="C76">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D76">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E76">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F76">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G76">
         <f t="shared" si="13"/>
-        <v>0.31818181818181823</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="H76">
         <f t="shared" si="14"/>
-        <v>0.45454545454545459</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="I76">
         <f t="shared" si="15"/>
-        <v>0.31818181818181823</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="J76">
         <f t="shared" si="16"/>
-        <v>1.0909090909090911</v>
+        <v>2.1818181818181821</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -5954,14 +5961,14 @@
       </c>
       <c r="T76">
         <f t="shared" si="17"/>
-        <v>10.101010101010102</v>
+        <v>20.202020202020204</v>
       </c>
       <c r="U76">
         <f t="shared" si="18"/>
-        <v>10.101010101010102</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>20.202020202020204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>322</v>
       </c>
@@ -5969,33 +5976,33 @@
         <v>25</v>
       </c>
       <c r="C77">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D77">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E77">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F77">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G77">
         <f t="shared" si="13"/>
-        <v>0.35000000000000003</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="H77">
         <f t="shared" si="14"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <f t="shared" si="15"/>
-        <v>0.35000000000000003</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="J77">
         <f t="shared" si="16"/>
-        <v>1.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -6026,14 +6033,14 @@
       </c>
       <c r="T77">
         <f t="shared" si="17"/>
-        <v>11.111111111111111</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="U77">
         <f t="shared" si="18"/>
-        <v>11.111111111111111</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>22.222222222222221</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>322</v>
       </c>
@@ -6041,33 +6048,33 @@
         <v>22.5</v>
       </c>
       <c r="C78">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D78">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E78">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F78">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G78">
         <f t="shared" si="13"/>
-        <v>0.3888888888888889</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="H78">
         <f t="shared" si="14"/>
-        <v>0.55555555555555558</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="I78">
         <f t="shared" si="15"/>
-        <v>0.3888888888888889</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="J78">
         <f t="shared" si="16"/>
-        <v>1.3333333333333333</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -6098,14 +6105,14 @@
       </c>
       <c r="T78">
         <f t="shared" si="17"/>
-        <v>12.345679012345679</v>
+        <v>24.691358024691358</v>
       </c>
       <c r="U78">
         <f t="shared" si="18"/>
-        <v>12.345679012345679</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>24.691358024691358</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>322</v>
       </c>
@@ -6113,33 +6120,33 @@
         <v>20</v>
       </c>
       <c r="C79">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D79">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E79">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F79">
         <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G79">
         <f t="shared" si="13"/>
-        <v>0.43750000000000006</v>
+        <v>0.87500000000000011</v>
       </c>
       <c r="H79">
         <f t="shared" si="14"/>
-        <v>0.62500000000000011</v>
+        <v>1.2500000000000002</v>
       </c>
       <c r="I79">
         <f t="shared" si="15"/>
-        <v>0.43750000000000006</v>
+        <v>0.87500000000000011</v>
       </c>
       <c r="J79">
         <f t="shared" si="16"/>
-        <v>1.5000000000000002</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -6170,14 +6177,14 @@
       </c>
       <c r="T79">
         <f t="shared" si="17"/>
-        <v>13.888888888888889</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="U79">
         <f t="shared" si="18"/>
-        <v>13.888888888888889</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>27.777777777777779</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>323</v>
       </c>
@@ -6185,33 +6192,33 @@
         <v>50</v>
       </c>
       <c r="C80">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D80">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E80">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F80">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G80">
         <f t="shared" si="13"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H80">
         <f t="shared" si="14"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I80">
         <f t="shared" si="15"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="J80">
         <f t="shared" si="16"/>
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="K80">
         <v>0</v>
@@ -6242,14 +6249,14 @@
       </c>
       <c r="T80">
         <f t="shared" si="17"/>
-        <v>6.4814814814814818</v>
+        <v>12.962962962962964</v>
       </c>
       <c r="U80">
         <f t="shared" si="18"/>
-        <v>6.4814814814814818</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.962962962962964</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>323</v>
       </c>
@@ -6257,33 +6264,33 @@
         <v>47.5</v>
       </c>
       <c r="C81">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D81">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E81">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F81">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G81">
         <f t="shared" si="13"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="H81">
         <f t="shared" si="14"/>
-        <v>0.26315789473684215</v>
+        <v>0.52631578947368429</v>
       </c>
       <c r="I81">
         <f t="shared" si="15"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="J81">
         <f t="shared" si="16"/>
-        <v>0.73684210526315796</v>
+        <v>1.4736842105263159</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -6314,14 +6321,14 @@
       </c>
       <c r="T81">
         <f t="shared" si="17"/>
-        <v>6.8226120857699808</v>
+        <v>13.645224171539962</v>
       </c>
       <c r="U81">
         <f t="shared" si="18"/>
-        <v>6.8226120857699808</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.645224171539962</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>323</v>
       </c>
@@ -6329,33 +6336,33 @@
         <v>45</v>
       </c>
       <c r="C82">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D82">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E82">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F82">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G82">
         <f t="shared" si="13"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H82">
         <f t="shared" si="14"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I82">
         <f t="shared" si="15"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J82">
         <f t="shared" si="16"/>
-        <v>0.77777777777777779</v>
+        <v>1.5555555555555556</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -6386,14 +6393,14 @@
       </c>
       <c r="T82">
         <f t="shared" si="17"/>
-        <v>7.2016460905349797</v>
+        <v>14.403292181069959</v>
       </c>
       <c r="U82">
         <f t="shared" si="18"/>
-        <v>7.2016460905349797</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.403292181069959</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>323</v>
       </c>
@@ -6401,33 +6408,33 @@
         <v>42.5</v>
       </c>
       <c r="C83">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D83">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E83">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F83">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G83">
         <f t="shared" si="13"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="H83">
         <f t="shared" si="14"/>
-        <v>0.29411764705882354</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="I83">
         <f t="shared" si="15"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J83">
         <f t="shared" si="16"/>
-        <v>0.82352941176470584</v>
+        <v>1.6470588235294117</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -6458,14 +6465,14 @@
       </c>
       <c r="T83">
         <f t="shared" si="17"/>
-        <v>7.6252723311546839</v>
+        <v>15.250544662309368</v>
       </c>
       <c r="U83">
         <f t="shared" si="18"/>
-        <v>7.6252723311546839</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.250544662309368</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>323</v>
       </c>
@@ -6473,33 +6480,33 @@
         <v>40</v>
       </c>
       <c r="C84">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D84">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E84">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F84">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G84">
         <f t="shared" si="13"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="H84">
         <f t="shared" si="14"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I84">
         <f t="shared" si="15"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="J84">
         <f t="shared" si="16"/>
-        <v>0.875</v>
+        <v>1.75</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -6530,14 +6537,14 @@
       </c>
       <c r="T84">
         <f t="shared" si="17"/>
-        <v>8.101851851851853</v>
+        <v>16.203703703703706</v>
       </c>
       <c r="U84">
         <f t="shared" si="18"/>
-        <v>8.101851851851853</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>16.203703703703706</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>323</v>
       </c>
@@ -6545,33 +6552,33 @@
         <v>37.5</v>
       </c>
       <c r="C85">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D85">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E85">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F85">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G85">
         <f t="shared" si="13"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H85">
         <f t="shared" si="14"/>
-        <v>0.33333333333333337</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I85">
         <f t="shared" si="15"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J85">
         <f t="shared" si="16"/>
-        <v>0.93333333333333335</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -6602,14 +6609,14 @@
       </c>
       <c r="T85">
         <f t="shared" si="17"/>
-        <v>8.6419753086419764</v>
+        <v>17.283950617283953</v>
       </c>
       <c r="U85">
         <f t="shared" si="18"/>
-        <v>8.6419753086419764</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>17.283950617283953</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>323</v>
       </c>
@@ -6617,33 +6624,33 @@
         <v>35</v>
       </c>
       <c r="C86">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D86">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E86">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F86">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G86">
         <f t="shared" si="13"/>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="H86">
         <f t="shared" si="14"/>
-        <v>0.35714285714285715</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I86">
         <f t="shared" si="15"/>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="J86">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -6674,14 +6681,14 @@
       </c>
       <c r="T86">
         <f t="shared" si="17"/>
-        <v>9.2592592592592595</v>
+        <v>18.518518518518519</v>
       </c>
       <c r="U86">
         <f t="shared" si="18"/>
-        <v>9.2592592592592595</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>18.518518518518519</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>323</v>
       </c>
@@ -6689,33 +6696,33 @@
         <v>32.5</v>
       </c>
       <c r="C87">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D87">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E87">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F87">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G87">
         <f t="shared" si="13"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="H87">
         <f t="shared" si="14"/>
-        <v>0.38461538461538464</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="I87">
         <f t="shared" si="15"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J87">
         <f t="shared" si="16"/>
-        <v>1.0769230769230771</v>
+        <v>2.1538461538461542</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -6746,14 +6753,14 @@
       </c>
       <c r="T87">
         <f t="shared" si="17"/>
-        <v>9.9715099715099722</v>
+        <v>19.943019943019944</v>
       </c>
       <c r="U87">
         <f t="shared" si="18"/>
-        <v>9.9715099715099722</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>19.943019943019944</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>323</v>
       </c>
@@ -6761,33 +6768,33 @@
         <v>30</v>
       </c>
       <c r="C88">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D88">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E88">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F88">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G88">
         <f t="shared" si="13"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="H88">
         <f t="shared" si="14"/>
-        <v>0.41666666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="I88">
         <f t="shared" si="15"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="J88">
         <f t="shared" si="16"/>
-        <v>1.1666666666666667</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="K88">
         <v>0</v>
@@ -6818,14 +6825,14 @@
       </c>
       <c r="T88">
         <f t="shared" si="17"/>
-        <v>10.80246913580247</v>
+        <v>21.60493827160494</v>
       </c>
       <c r="U88">
         <f t="shared" si="18"/>
-        <v>10.80246913580247</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>21.60493827160494</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>323</v>
       </c>
@@ -6833,33 +6840,33 @@
         <v>27.5</v>
       </c>
       <c r="C89">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D89">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E89">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F89">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G89">
         <f t="shared" si="13"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="H89">
         <f t="shared" si="14"/>
-        <v>0.45454545454545459</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="I89">
         <f t="shared" si="15"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="J89">
         <f t="shared" si="16"/>
-        <v>1.2727272727272729</v>
+        <v>2.5454545454545459</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -6890,14 +6897,14 @@
       </c>
       <c r="T89">
         <f t="shared" si="17"/>
-        <v>11.784511784511787</v>
+        <v>23.569023569023575</v>
       </c>
       <c r="U89">
         <f t="shared" si="18"/>
-        <v>11.784511784511787</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>23.569023569023575</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>323</v>
       </c>
@@ -6905,33 +6912,33 @@
         <v>25</v>
       </c>
       <c r="C90">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D90">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E90">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F90">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G90">
         <f t="shared" si="13"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H90">
         <f t="shared" si="14"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <f t="shared" si="15"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J90">
         <f t="shared" si="16"/>
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="K90">
         <v>0</v>
@@ -6962,14 +6969,14 @@
       </c>
       <c r="T90">
         <f t="shared" si="17"/>
-        <v>12.962962962962964</v>
+        <v>25.925925925925927</v>
       </c>
       <c r="U90">
         <f t="shared" si="18"/>
-        <v>12.962962962962964</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>25.925925925925927</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>323</v>
       </c>
@@ -6977,33 +6984,33 @@
         <v>22.5</v>
       </c>
       <c r="C91">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D91">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E91">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F91">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G91">
         <f t="shared" si="13"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <f t="shared" si="14"/>
-        <v>0.55555555555555558</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="I91">
         <f t="shared" si="15"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J91">
         <f t="shared" si="16"/>
-        <v>1.5555555555555556</v>
+        <v>3.1111111111111112</v>
       </c>
       <c r="K91">
         <v>0</v>
@@ -7034,14 +7041,14 @@
       </c>
       <c r="T91">
         <f t="shared" si="17"/>
-        <v>14.403292181069959</v>
+        <v>28.806584362139919</v>
       </c>
       <c r="U91">
         <f t="shared" si="18"/>
-        <v>14.403292181069959</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>28.806584362139919</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>323</v>
       </c>
@@ -7049,33 +7056,33 @@
         <v>20</v>
       </c>
       <c r="C92">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D92">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E92">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F92">
         <f t="shared" si="19"/>
-        <v>1166.6666666666667</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="G92">
         <f t="shared" si="13"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="H92">
         <f t="shared" si="14"/>
-        <v>0.62500000000000011</v>
+        <v>1.2500000000000002</v>
       </c>
       <c r="I92">
         <f t="shared" si="15"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="J92">
         <f t="shared" si="16"/>
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -7106,11 +7113,11 @@
       </c>
       <c r="T92">
         <f t="shared" si="17"/>
-        <v>16.203703703703706</v>
+        <v>32.407407407407412</v>
       </c>
       <c r="U92">
         <f t="shared" si="18"/>
-        <v>16.203703703703706</v>
+        <v>32.407407407407412</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7121,33 +7128,33 @@
         <v>50</v>
       </c>
       <c r="C93">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D93">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E93">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F93">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G93">
         <f t="shared" si="13"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="H93">
         <f t="shared" si="14"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I93">
         <f t="shared" si="15"/>
-        <v>0.125</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="J93">
         <f t="shared" si="16"/>
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="K93">
         <v>0</v>
@@ -7178,11 +7185,11 @@
       </c>
       <c r="T93">
         <f t="shared" si="17"/>
-        <v>4.6296296296296298</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U93">
         <f t="shared" si="18"/>
-        <v>4.6296296296296298</v>
+        <v>11.111111111111111</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7193,33 +7200,33 @@
         <v>47.5</v>
       </c>
       <c r="C94">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D94">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E94">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F94">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G94">
         <f t="shared" si="13"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="H94">
         <f t="shared" si="14"/>
-        <v>0.26315789473684215</v>
+        <v>0.52631578947368429</v>
       </c>
       <c r="I94">
         <f t="shared" si="15"/>
-        <v>0.13157894736842107</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="J94">
         <f t="shared" si="16"/>
-        <v>0.52631578947368429</v>
+        <v>1.2631578947368423</v>
       </c>
       <c r="K94">
         <v>0</v>
@@ -7250,11 +7257,11 @@
       </c>
       <c r="T94">
         <f t="shared" si="17"/>
-        <v>4.8732943469785583</v>
+        <v>11.695906432748538</v>
       </c>
       <c r="U94">
         <f t="shared" si="18"/>
-        <v>4.8732943469785583</v>
+        <v>11.695906432748538</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7265,33 +7272,33 @@
         <v>45</v>
       </c>
       <c r="C95">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D95">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E95">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F95">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G95">
         <f t="shared" si="13"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="H95">
         <f t="shared" si="14"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I95">
         <f t="shared" si="15"/>
-        <v>0.1388888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="J95">
         <f t="shared" si="16"/>
-        <v>0.55555555555555558</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -7322,11 +7329,11 @@
       </c>
       <c r="T95">
         <f t="shared" si="17"/>
-        <v>5.1440329218106999</v>
+        <v>12.345679012345679</v>
       </c>
       <c r="U95">
         <f t="shared" si="18"/>
-        <v>5.1440329218106999</v>
+        <v>12.345679012345679</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7337,33 +7344,33 @@
         <v>42.5</v>
       </c>
       <c r="C96">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D96">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E96">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F96">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G96">
         <f t="shared" si="13"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="H96">
         <f t="shared" si="14"/>
-        <v>0.29411764705882354</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="I96">
         <f t="shared" si="15"/>
-        <v>0.14705882352941177</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J96">
         <f t="shared" si="16"/>
-        <v>0.58823529411764708</v>
+        <v>1.4117647058823528</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -7394,11 +7401,11 @@
       </c>
       <c r="T96">
         <f t="shared" si="17"/>
-        <v>5.4466230936819171</v>
+        <v>13.071895424836603</v>
       </c>
       <c r="U96">
         <f t="shared" si="18"/>
-        <v>5.4466230936819171</v>
+        <v>13.071895424836603</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7409,33 +7416,33 @@
         <v>40</v>
       </c>
       <c r="C97">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D97">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E97">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F97">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G97">
         <f t="shared" si="13"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="H97">
         <f t="shared" si="14"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I97">
         <f t="shared" si="15"/>
-        <v>0.15625000000000003</v>
+        <v>0.5625</v>
       </c>
       <c r="J97">
         <f t="shared" si="16"/>
-        <v>0.62500000000000011</v>
+        <v>1.5000000000000002</v>
       </c>
       <c r="K97">
         <v>0</v>
@@ -7466,11 +7473,11 @@
       </c>
       <c r="T97">
         <f t="shared" si="17"/>
-        <v>5.7870370370370381</v>
+        <v>13.888888888888889</v>
       </c>
       <c r="U97">
         <f t="shared" si="18"/>
-        <v>5.7870370370370381</v>
+        <v>13.888888888888889</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7481,33 +7488,33 @@
         <v>37.5</v>
       </c>
       <c r="C98">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D98">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E98">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F98">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G98">
         <f t="shared" ref="G98:G129" si="20">C98/(120*$B98*1000/3600)</f>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="H98">
         <f t="shared" ref="H98:H129" si="21">D98/(120*$B98*1000/3600)</f>
-        <v>0.33333333333333337</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I98">
         <f t="shared" ref="I98:I129" si="22">E98/(120*$B98*1000/3600)</f>
-        <v>0.16666666666666669</v>
+        <v>0.6</v>
       </c>
       <c r="J98">
         <f t="shared" ref="J98:J129" si="23">SUM(G98:I98)</f>
-        <v>0.66666666666666674</v>
+        <v>1.6</v>
       </c>
       <c r="K98">
         <v>0</v>
@@ -7538,11 +7545,11 @@
       </c>
       <c r="T98">
         <f t="shared" ref="T98:T129" si="24">F98/B98*1000/3600</f>
-        <v>6.1728395061728403</v>
+        <v>14.814814814814815</v>
       </c>
       <c r="U98">
         <f t="shared" ref="U98:U129" si="25">S98+T98</f>
-        <v>6.1728395061728403</v>
+        <v>14.814814814814815</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7553,33 +7560,33 @@
         <v>35</v>
       </c>
       <c r="C99">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D99">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E99">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F99">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G99">
         <f t="shared" si="20"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="H99">
         <f t="shared" si="21"/>
-        <v>0.35714285714285715</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I99">
         <f t="shared" si="22"/>
-        <v>0.17857142857142858</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="J99">
         <f t="shared" si="23"/>
-        <v>0.7142857142857143</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="K99">
         <v>0</v>
@@ -7610,11 +7617,11 @@
       </c>
       <c r="T99">
         <f t="shared" si="24"/>
-        <v>6.6137566137566139</v>
+        <v>15.873015873015873</v>
       </c>
       <c r="U99">
         <f t="shared" si="25"/>
-        <v>6.6137566137566139</v>
+        <v>15.873015873015873</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7625,33 +7632,33 @@
         <v>32.5</v>
       </c>
       <c r="C100">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D100">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E100">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F100">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G100">
         <f t="shared" si="20"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H100">
         <f t="shared" si="21"/>
-        <v>0.38461538461538464</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="I100">
         <f t="shared" si="22"/>
-        <v>0.19230769230769232</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J100">
         <f t="shared" si="23"/>
-        <v>0.76923076923076927</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="K100">
         <v>0</v>
@@ -7682,11 +7689,11 @@
       </c>
       <c r="T100">
         <f t="shared" si="24"/>
-        <v>7.1225071225071224</v>
+        <v>17.094017094017094</v>
       </c>
       <c r="U100">
         <f t="shared" si="25"/>
-        <v>7.1225071225071224</v>
+        <v>17.094017094017094</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7697,33 +7704,33 @@
         <v>30</v>
       </c>
       <c r="C101">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D101">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E101">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F101">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G101">
         <f t="shared" si="20"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H101">
         <f t="shared" si="21"/>
-        <v>0.41666666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="I101">
         <f t="shared" si="22"/>
-        <v>0.20833333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="J101">
         <f t="shared" si="23"/>
-        <v>0.83333333333333337</v>
+        <v>2</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -7754,11 +7761,11 @@
       </c>
       <c r="T101">
         <f t="shared" si="24"/>
-        <v>7.716049382716049</v>
+        <v>18.518518518518519</v>
       </c>
       <c r="U101">
         <f t="shared" si="25"/>
-        <v>7.716049382716049</v>
+        <v>18.518518518518519</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7769,33 +7776,33 @@
         <v>27.5</v>
       </c>
       <c r="C102">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D102">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E102">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F102">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G102">
         <f t="shared" si="20"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="H102">
         <f t="shared" si="21"/>
-        <v>0.45454545454545459</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="I102">
         <f t="shared" si="22"/>
-        <v>0.22727272727272729</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="J102">
         <f t="shared" si="23"/>
-        <v>0.90909090909090917</v>
+        <v>2.1818181818181821</v>
       </c>
       <c r="K102">
         <v>0</v>
@@ -7826,11 +7833,11 @@
       </c>
       <c r="T102">
         <f t="shared" si="24"/>
-        <v>8.4175084175084169</v>
+        <v>20.202020202020204</v>
       </c>
       <c r="U102">
         <f t="shared" si="25"/>
-        <v>8.4175084175084169</v>
+        <v>20.202020202020204</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7841,33 +7848,33 @@
         <v>25</v>
       </c>
       <c r="C103">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D103">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E103">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F103">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G103">
         <f t="shared" si="20"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H103">
         <f t="shared" si="21"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I103">
         <f t="shared" si="22"/>
-        <v>0.25</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J103">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="K103">
         <v>0</v>
@@ -7898,11 +7905,11 @@
       </c>
       <c r="T103">
         <f t="shared" si="24"/>
-        <v>9.2592592592592595</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="U103">
         <f t="shared" si="25"/>
-        <v>9.2592592592592595</v>
+        <v>22.222222222222221</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7913,33 +7920,33 @@
         <v>22.5</v>
       </c>
       <c r="C104">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D104">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E104">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F104">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G104">
         <f t="shared" si="20"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H104">
         <f t="shared" si="21"/>
-        <v>0.55555555555555558</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="I104">
         <f t="shared" si="22"/>
-        <v>0.27777777777777779</v>
+        <v>1</v>
       </c>
       <c r="J104">
         <f t="shared" si="23"/>
-        <v>1.1111111111111112</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="K104">
         <v>0</v>
@@ -7970,11 +7977,11 @@
       </c>
       <c r="T104">
         <f t="shared" si="24"/>
-        <v>10.2880658436214</v>
+        <v>24.691358024691358</v>
       </c>
       <c r="U104">
         <f t="shared" si="25"/>
-        <v>10.2880658436214</v>
+        <v>24.691358024691358</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7985,33 +7992,33 @@
         <v>20</v>
       </c>
       <c r="C105">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D105">
-        <v>416.66666666666669</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="E105">
-        <v>208.33333333333334</v>
+        <v>750</v>
       </c>
       <c r="F105">
         <f t="shared" si="19"/>
-        <v>833.33333333333337</v>
+        <v>2000</v>
       </c>
       <c r="G105">
         <f t="shared" si="20"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="H105">
         <f t="shared" si="21"/>
-        <v>0.62500000000000011</v>
+        <v>1.2500000000000002</v>
       </c>
       <c r="I105">
         <f t="shared" si="22"/>
-        <v>0.31250000000000006</v>
+        <v>1.125</v>
       </c>
       <c r="J105">
         <f t="shared" si="23"/>
-        <v>1.2500000000000002</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="K105">
         <v>0</v>
@@ -8042,14 +8049,14 @@
       </c>
       <c r="T105">
         <f t="shared" si="24"/>
-        <v>11.574074074074076</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="U105">
         <f t="shared" si="25"/>
-        <v>11.574074074074076</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>27.777777777777779</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106">
         <v>331</v>
       </c>
@@ -8057,33 +8064,33 @@
         <v>50</v>
       </c>
       <c r="C106">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D106">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E106">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F106">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G106">
         <f t="shared" si="20"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="H106">
         <f t="shared" si="21"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="I106">
         <f t="shared" si="22"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="J106">
         <f t="shared" si="23"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -8114,14 +8121,14 @@
       </c>
       <c r="T106">
         <f t="shared" si="24"/>
-        <v>3.4722222222222223</v>
+        <v>6.9444444444444446</v>
       </c>
       <c r="U106">
         <f t="shared" si="25"/>
-        <v>3.4722222222222223</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>6.9444444444444446</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107">
         <v>331</v>
       </c>
@@ -8129,33 +8136,33 @@
         <v>47.5</v>
       </c>
       <c r="C107">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D107">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E107">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F107">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G107">
         <f t="shared" si="20"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="H107">
         <f t="shared" si="21"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="I107">
         <f t="shared" si="22"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="J107">
         <f t="shared" si="23"/>
-        <v>0.39473684210526322</v>
+        <v>0.78947368421052644</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -8186,14 +8193,14 @@
       </c>
       <c r="T107">
         <f t="shared" si="24"/>
-        <v>3.6549707602339181</v>
+        <v>7.3099415204678362</v>
       </c>
       <c r="U107">
         <f t="shared" si="25"/>
-        <v>3.6549707602339181</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>7.3099415204678362</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108">
         <v>331</v>
       </c>
@@ -8201,33 +8208,33 @@
         <v>45</v>
       </c>
       <c r="C108">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D108">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E108">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F108">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G108">
         <f t="shared" si="20"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="H108">
         <f t="shared" si="21"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="I108">
         <f t="shared" si="22"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="J108">
         <f t="shared" si="23"/>
-        <v>0.41666666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="K108">
         <v>0</v>
@@ -8258,14 +8265,14 @@
       </c>
       <c r="T108">
         <f t="shared" si="24"/>
-        <v>3.8580246913580245</v>
+        <v>7.716049382716049</v>
       </c>
       <c r="U108">
         <f t="shared" si="25"/>
-        <v>3.8580246913580245</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>7.716049382716049</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109">
         <v>331</v>
       </c>
@@ -8273,33 +8280,33 @@
         <v>42.5</v>
       </c>
       <c r="C109">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D109">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E109">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F109">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G109">
         <f t="shared" si="20"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="H109">
         <f t="shared" si="21"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I109">
         <f t="shared" si="22"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="J109">
         <f t="shared" si="23"/>
-        <v>0.44117647058823528</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="K109">
         <v>0</v>
@@ -8330,14 +8337,14 @@
       </c>
       <c r="T109">
         <f t="shared" si="24"/>
-        <v>4.0849673202614376</v>
+        <v>8.1699346405228752</v>
       </c>
       <c r="U109">
         <f t="shared" si="25"/>
-        <v>4.0849673202614376</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>8.1699346405228752</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110">
         <v>331</v>
       </c>
@@ -8345,33 +8352,33 @@
         <v>40</v>
       </c>
       <c r="C110">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D110">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E110">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F110">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G110">
         <f t="shared" si="20"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="H110">
         <f t="shared" si="21"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="I110">
         <f t="shared" si="22"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="J110">
         <f t="shared" si="23"/>
-        <v>0.46875000000000011</v>
+        <v>0.93750000000000022</v>
       </c>
       <c r="K110">
         <v>0</v>
@@ -8402,14 +8409,14 @@
       </c>
       <c r="T110">
         <f t="shared" si="24"/>
-        <v>4.3402777777777777</v>
+        <v>8.6805555555555554</v>
       </c>
       <c r="U110">
         <f t="shared" si="25"/>
-        <v>4.3402777777777777</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>8.6805555555555554</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111">
         <v>331</v>
       </c>
@@ -8417,33 +8424,33 @@
         <v>37.5</v>
       </c>
       <c r="C111">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D111">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E111">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F111">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G111">
         <f t="shared" si="20"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="H111">
         <f t="shared" si="21"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="I111">
         <f t="shared" si="22"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J111">
         <f t="shared" si="23"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K111">
         <v>0</v>
@@ -8474,14 +8481,14 @@
       </c>
       <c r="T111">
         <f t="shared" si="24"/>
-        <v>4.6296296296296298</v>
+        <v>9.2592592592592595</v>
       </c>
       <c r="U111">
         <f t="shared" si="25"/>
-        <v>4.6296296296296298</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.2592592592592595</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112">
         <v>331</v>
       </c>
@@ -8489,33 +8496,33 @@
         <v>35</v>
       </c>
       <c r="C112">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D112">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E112">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F112">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G112">
         <f t="shared" si="20"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="H112">
         <f t="shared" si="21"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="I112">
         <f t="shared" si="22"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="J112">
         <f t="shared" si="23"/>
-        <v>0.5357142857142857</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="K112">
         <v>0</v>
@@ -8546,14 +8553,14 @@
       </c>
       <c r="T112">
         <f t="shared" si="24"/>
-        <v>4.9603174603174605</v>
+        <v>9.9206349206349209</v>
       </c>
       <c r="U112">
         <f t="shared" si="25"/>
-        <v>4.9603174603174605</v>
-      </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.9206349206349209</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113">
         <v>331</v>
       </c>
@@ -8561,33 +8568,33 @@
         <v>32.5</v>
       </c>
       <c r="C113">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D113">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E113">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F113">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G113">
         <f t="shared" si="20"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H113">
         <f t="shared" si="21"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="I113">
         <f t="shared" si="22"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="J113">
         <f t="shared" si="23"/>
-        <v>0.57692307692307698</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -8618,14 +8625,14 @@
       </c>
       <c r="T113">
         <f t="shared" si="24"/>
-        <v>5.3418803418803416</v>
+        <v>10.683760683760683</v>
       </c>
       <c r="U113">
         <f t="shared" si="25"/>
-        <v>5.3418803418803416</v>
-      </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.683760683760683</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114">
         <v>331</v>
       </c>
@@ -8633,33 +8640,33 @@
         <v>30</v>
       </c>
       <c r="C114">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D114">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E114">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F114">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G114">
         <f t="shared" si="20"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H114">
         <f t="shared" si="21"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I114">
         <f t="shared" si="22"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J114">
         <f t="shared" si="23"/>
-        <v>0.625</v>
+        <v>1.25</v>
       </c>
       <c r="K114">
         <v>0</v>
@@ -8690,14 +8697,14 @@
       </c>
       <c r="T114">
         <f t="shared" si="24"/>
-        <v>5.7870370370370363</v>
+        <v>11.574074074074073</v>
       </c>
       <c r="U114">
         <f t="shared" si="25"/>
-        <v>5.7870370370370363</v>
-      </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.574074074074073</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A115">
         <v>331</v>
       </c>
@@ -8705,33 +8712,33 @@
         <v>27.5</v>
       </c>
       <c r="C115">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D115">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E115">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F115">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G115">
         <f t="shared" si="20"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="H115">
         <f t="shared" si="21"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="I115">
         <f t="shared" si="22"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="J115">
         <f t="shared" si="23"/>
-        <v>0.68181818181818188</v>
+        <v>1.3636363636363638</v>
       </c>
       <c r="K115">
         <v>0</v>
@@ -8762,14 +8769,14 @@
       </c>
       <c r="T115">
         <f t="shared" si="24"/>
-        <v>6.3131313131313131</v>
+        <v>12.626262626262626</v>
       </c>
       <c r="U115">
         <f t="shared" si="25"/>
-        <v>6.3131313131313131</v>
-      </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.626262626262626</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116">
         <v>331</v>
       </c>
@@ -8777,33 +8784,33 @@
         <v>25</v>
       </c>
       <c r="C116">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D116">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E116">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F116">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G116">
         <f t="shared" si="20"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H116">
         <f t="shared" si="21"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I116">
         <f t="shared" si="22"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J116">
         <f t="shared" si="23"/>
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="K116">
         <v>0</v>
@@ -8834,14 +8841,14 @@
       </c>
       <c r="T116">
         <f t="shared" si="24"/>
-        <v>6.9444444444444446</v>
+        <v>13.888888888888889</v>
       </c>
       <c r="U116">
         <f t="shared" si="25"/>
-        <v>6.9444444444444446</v>
-      </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.888888888888889</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117">
         <v>331</v>
       </c>
@@ -8849,33 +8856,33 @@
         <v>22.5</v>
       </c>
       <c r="C117">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D117">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E117">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F117">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G117">
         <f t="shared" si="20"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H117">
         <f t="shared" si="21"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I117">
         <f t="shared" si="22"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="J117">
         <f t="shared" si="23"/>
-        <v>0.83333333333333337</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -8906,14 +8913,14 @@
       </c>
       <c r="T117">
         <f t="shared" si="24"/>
-        <v>7.716049382716049</v>
+        <v>15.432098765432098</v>
       </c>
       <c r="U117">
         <f t="shared" si="25"/>
-        <v>7.716049382716049</v>
-      </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.432098765432098</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118">
         <v>331</v>
       </c>
@@ -8921,33 +8928,33 @@
         <v>20</v>
       </c>
       <c r="C118">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D118">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E118">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="F118">
         <f t="shared" si="19"/>
-        <v>625</v>
+        <v>1250</v>
       </c>
       <c r="G118">
         <f t="shared" si="20"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="H118">
         <f t="shared" si="21"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I118">
         <f t="shared" si="22"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="J118">
         <f t="shared" si="23"/>
-        <v>0.93750000000000022</v>
+        <v>1.8750000000000004</v>
       </c>
       <c r="K118">
         <v>0</v>
@@ -8978,14 +8985,14 @@
       </c>
       <c r="T118">
         <f t="shared" si="24"/>
-        <v>8.6805555555555554</v>
+        <v>17.361111111111111</v>
       </c>
       <c r="U118">
         <f t="shared" si="25"/>
-        <v>8.6805555555555554</v>
-      </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>17.361111111111111</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119">
         <v>332</v>
       </c>
@@ -8993,33 +9000,33 @@
         <v>50</v>
       </c>
       <c r="C119">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D119">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E119">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F119">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G119">
         <f t="shared" si="20"/>
-        <v>0.17500000000000002</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="H119">
         <f t="shared" si="21"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="I119">
         <f t="shared" si="22"/>
-        <v>0.17500000000000002</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="J119">
         <f t="shared" si="23"/>
-        <v>0.47500000000000009</v>
+        <v>0.95000000000000018</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -9050,14 +9057,14 @@
       </c>
       <c r="T119">
         <f t="shared" si="24"/>
-        <v>4.3981481481481488</v>
+        <v>8.7962962962962976</v>
       </c>
       <c r="U119">
         <f t="shared" si="25"/>
-        <v>4.3981481481481488</v>
-      </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>8.7962962962962976</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A120">
         <v>332</v>
       </c>
@@ -9065,33 +9072,33 @@
         <v>47.5</v>
       </c>
       <c r="C120">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D120">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E120">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F120">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G120">
         <f t="shared" si="20"/>
-        <v>0.18421052631578949</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="H120">
         <f t="shared" si="21"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="I120">
         <f t="shared" si="22"/>
-        <v>0.18421052631578949</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="J120">
         <f t="shared" si="23"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K120">
         <v>0</v>
@@ -9122,14 +9129,14 @@
       </c>
       <c r="T120">
         <f t="shared" si="24"/>
-        <v>4.6296296296296298</v>
+        <v>9.2592592592592595</v>
       </c>
       <c r="U120">
         <f t="shared" si="25"/>
-        <v>4.6296296296296298</v>
-      </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.2592592592592595</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121">
         <v>332</v>
       </c>
@@ -9137,33 +9144,33 @@
         <v>45</v>
       </c>
       <c r="C121">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D121">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E121">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F121">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G121">
         <f t="shared" si="20"/>
-        <v>0.19444444444444445</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="H121">
         <f t="shared" si="21"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="I121">
         <f t="shared" si="22"/>
-        <v>0.19444444444444445</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J121">
         <f t="shared" si="23"/>
-        <v>0.52777777777777779</v>
+        <v>1.0555555555555556</v>
       </c>
       <c r="K121">
         <v>0</v>
@@ -9194,14 +9201,14 @@
       </c>
       <c r="T121">
         <f t="shared" si="24"/>
-        <v>4.8868312757201648</v>
+        <v>9.7736625514403297</v>
       </c>
       <c r="U121">
         <f t="shared" si="25"/>
-        <v>4.8868312757201648</v>
-      </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.7736625514403297</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122">
         <v>332</v>
       </c>
@@ -9209,33 +9216,33 @@
         <v>42.5</v>
       </c>
       <c r="C122">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D122">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E122">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F122">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G122">
         <f t="shared" si="20"/>
-        <v>0.20588235294117646</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="H122">
         <f t="shared" si="21"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I122">
         <f t="shared" si="22"/>
-        <v>0.20588235294117646</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="J122">
         <f t="shared" si="23"/>
-        <v>0.55882352941176472</v>
+        <v>1.1176470588235294</v>
       </c>
       <c r="K122">
         <v>0</v>
@@ -9266,14 +9273,14 @@
       </c>
       <c r="T122">
         <f t="shared" si="24"/>
-        <v>5.1742919389978219</v>
+        <v>10.348583877995644</v>
       </c>
       <c r="U122">
         <f t="shared" si="25"/>
-        <v>5.1742919389978219</v>
-      </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.348583877995644</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123">
         <v>332</v>
       </c>
@@ -9281,33 +9288,33 @@
         <v>40</v>
       </c>
       <c r="C123">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D123">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E123">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F123">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G123">
         <f t="shared" si="20"/>
-        <v>0.21875000000000003</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="H123">
         <f t="shared" si="21"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="I123">
         <f t="shared" si="22"/>
-        <v>0.21875000000000003</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="J123">
         <f t="shared" si="23"/>
-        <v>0.59375000000000011</v>
+        <v>1.1875000000000002</v>
       </c>
       <c r="K123">
         <v>0</v>
@@ -9338,14 +9345,14 @@
       </c>
       <c r="T123">
         <f t="shared" si="24"/>
-        <v>5.4976851851851851</v>
+        <v>10.99537037037037</v>
       </c>
       <c r="U123">
         <f t="shared" si="25"/>
-        <v>5.4976851851851851</v>
-      </c>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.99537037037037</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A124">
         <v>332</v>
       </c>
@@ -9353,33 +9360,33 @@
         <v>37.5</v>
       </c>
       <c r="C124">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D124">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E124">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F124">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G124">
         <f t="shared" si="20"/>
-        <v>0.23333333333333334</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="H124">
         <f t="shared" si="21"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="I124">
         <f t="shared" si="22"/>
-        <v>0.23333333333333334</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="J124">
         <f t="shared" si="23"/>
-        <v>0.6333333333333333</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="K124">
         <v>0</v>
@@ -9410,14 +9417,14 @@
       </c>
       <c r="T124">
         <f t="shared" si="24"/>
-        <v>5.8641975308641978</v>
+        <v>11.728395061728396</v>
       </c>
       <c r="U124">
         <f t="shared" si="25"/>
-        <v>5.8641975308641978</v>
-      </c>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.728395061728396</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125">
         <v>332</v>
       </c>
@@ -9425,33 +9432,33 @@
         <v>35</v>
       </c>
       <c r="C125">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D125">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E125">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F125">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G125">
         <f t="shared" si="20"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H125">
         <f t="shared" si="21"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="I125">
         <f t="shared" si="22"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J125">
         <f t="shared" si="23"/>
-        <v>0.6785714285714286</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="K125">
         <v>0</v>
@@ -9482,14 +9489,14 @@
       </c>
       <c r="T125">
         <f t="shared" si="24"/>
-        <v>6.2830687830687841</v>
+        <v>12.566137566137568</v>
       </c>
       <c r="U125">
         <f t="shared" si="25"/>
-        <v>6.2830687830687841</v>
-      </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.566137566137568</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126">
         <v>332</v>
       </c>
@@ -9497,33 +9504,33 @@
         <v>32.5</v>
       </c>
       <c r="C126">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D126">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E126">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F126">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G126">
         <f t="shared" si="20"/>
-        <v>0.26923076923076927</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="H126">
         <f t="shared" si="21"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="I126">
         <f t="shared" si="22"/>
-        <v>0.26923076923076927</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="J126">
         <f t="shared" si="23"/>
-        <v>0.73076923076923084</v>
+        <v>1.4615384615384617</v>
       </c>
       <c r="K126">
         <v>0</v>
@@ -9554,14 +9561,14 @@
       </c>
       <c r="T126">
         <f t="shared" si="24"/>
-        <v>6.7663817663817678</v>
+        <v>13.532763532763536</v>
       </c>
       <c r="U126">
         <f t="shared" si="25"/>
-        <v>6.7663817663817678</v>
-      </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.532763532763536</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127">
         <v>332</v>
       </c>
@@ -9569,33 +9576,33 @@
         <v>30</v>
       </c>
       <c r="C127">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D127">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E127">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F127">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G127">
         <f t="shared" si="20"/>
-        <v>0.29166666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H127">
         <f t="shared" si="21"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I127">
         <f t="shared" si="22"/>
-        <v>0.29166666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J127">
         <f t="shared" si="23"/>
-        <v>0.79166666666666674</v>
+        <v>1.5833333333333335</v>
       </c>
       <c r="K127">
         <v>0</v>
@@ -9626,14 +9633,14 @@
       </c>
       <c r="T127">
         <f t="shared" si="24"/>
-        <v>7.3302469135802486</v>
+        <v>14.660493827160497</v>
       </c>
       <c r="U127">
         <f t="shared" si="25"/>
-        <v>7.3302469135802486</v>
-      </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.660493827160497</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A128">
         <v>332</v>
       </c>
@@ -9641,33 +9648,33 @@
         <v>27.5</v>
       </c>
       <c r="C128">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D128">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E128">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F128">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G128">
         <f t="shared" si="20"/>
-        <v>0.31818181818181823</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="H128">
         <f t="shared" si="21"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="I128">
         <f t="shared" si="22"/>
-        <v>0.31818181818181823</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="J128">
         <f t="shared" si="23"/>
-        <v>0.86363636363636376</v>
+        <v>1.7272727272727275</v>
       </c>
       <c r="K128">
         <v>0</v>
@@ -9698,14 +9705,14 @@
       </c>
       <c r="T128">
         <f t="shared" si="24"/>
-        <v>7.9966329966329965</v>
+        <v>15.993265993265993</v>
       </c>
       <c r="U128">
         <f t="shared" si="25"/>
-        <v>7.9966329966329965</v>
-      </c>
-    </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.993265993265993</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129">
         <v>332</v>
       </c>
@@ -9713,33 +9720,33 @@
         <v>25</v>
       </c>
       <c r="C129">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D129">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E129">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F129">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G129">
         <f t="shared" si="20"/>
-        <v>0.35000000000000003</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="H129">
         <f t="shared" si="21"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I129">
         <f t="shared" si="22"/>
-        <v>0.35000000000000003</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="J129">
         <f t="shared" si="23"/>
-        <v>0.95000000000000018</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -9770,14 +9777,14 @@
       </c>
       <c r="T129">
         <f t="shared" si="24"/>
-        <v>8.7962962962962976</v>
+        <v>17.592592592592595</v>
       </c>
       <c r="U129">
         <f t="shared" si="25"/>
-        <v>8.7962962962962976</v>
-      </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>17.592592592592595</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130">
         <v>332</v>
       </c>
@@ -9785,33 +9792,33 @@
         <v>22.5</v>
       </c>
       <c r="C130">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D130">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E130">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F130">
         <f t="shared" si="19"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G130">
         <f t="shared" ref="G130:G157" si="26">C130/(120*$B130*1000/3600)</f>
-        <v>0.3888888888888889</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="H130">
         <f t="shared" ref="H130:H157" si="27">D130/(120*$B130*1000/3600)</f>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I130">
         <f t="shared" ref="I130:I157" si="28">E130/(120*$B130*1000/3600)</f>
-        <v>0.3888888888888889</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="J130">
         <f t="shared" ref="J130:J157" si="29">SUM(G130:I130)</f>
-        <v>1.0555555555555556</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -9842,14 +9849,14 @@
       </c>
       <c r="T130">
         <f t="shared" ref="T130:T157" si="30">F130/B130*1000/3600</f>
-        <v>9.7736625514403297</v>
+        <v>19.547325102880659</v>
       </c>
       <c r="U130">
         <f t="shared" ref="U130:U157" si="31">S130+T130</f>
-        <v>9.7736625514403297</v>
-      </c>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>19.547325102880659</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131">
         <v>332</v>
       </c>
@@ -9857,33 +9864,33 @@
         <v>20</v>
       </c>
       <c r="C131">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="D131">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E131">
-        <v>291.66666666666669</v>
+        <v>583.33333333333337</v>
       </c>
       <c r="F131">
         <f t="shared" ref="F131:F157" si="32">SUM(C131:E131)</f>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G131">
         <f t="shared" si="26"/>
-        <v>0.43750000000000006</v>
+        <v>0.87500000000000011</v>
       </c>
       <c r="H131">
         <f t="shared" si="27"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I131">
         <f t="shared" si="28"/>
-        <v>0.43750000000000006</v>
+        <v>0.87500000000000011</v>
       </c>
       <c r="J131">
         <f t="shared" si="29"/>
-        <v>1.1875000000000002</v>
+        <v>2.3750000000000004</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -9914,14 +9921,14 @@
       </c>
       <c r="T131">
         <f t="shared" si="30"/>
-        <v>10.99537037037037</v>
+        <v>21.99074074074074</v>
       </c>
       <c r="U131">
         <f t="shared" si="31"/>
-        <v>10.99537037037037</v>
-      </c>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>21.99074074074074</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132">
         <v>333</v>
       </c>
@@ -9929,33 +9936,33 @@
         <v>50</v>
       </c>
       <c r="C132">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D132">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E132">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F132">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G132">
         <f t="shared" si="26"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H132">
         <f t="shared" si="27"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="I132">
         <f t="shared" si="28"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="J132">
         <f t="shared" si="29"/>
-        <v>0.57499999999999996</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -9986,14 +9993,14 @@
       </c>
       <c r="T132">
         <f t="shared" si="30"/>
-        <v>5.3240740740740744</v>
+        <v>10.648148148148149</v>
       </c>
       <c r="U132">
         <f t="shared" si="31"/>
-        <v>5.3240740740740744</v>
-      </c>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.648148148148149</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133">
         <v>333</v>
       </c>
@@ -10001,33 +10008,33 @@
         <v>47.5</v>
       </c>
       <c r="C133">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D133">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E133">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F133">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G133">
         <f t="shared" si="26"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="H133">
         <f t="shared" si="27"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="I133">
         <f t="shared" si="28"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="J133">
         <f t="shared" si="29"/>
-        <v>0.60526315789473695</v>
+        <v>1.2105263157894739</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -10058,14 +10065,14 @@
       </c>
       <c r="T133">
         <f t="shared" si="30"/>
-        <v>5.6042884990253414</v>
+        <v>11.208576998050683</v>
       </c>
       <c r="U133">
         <f t="shared" si="31"/>
-        <v>5.6042884990253414</v>
-      </c>
-    </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.208576998050683</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134">
         <v>333</v>
       </c>
@@ -10073,33 +10080,33 @@
         <v>45</v>
       </c>
       <c r="C134">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D134">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E134">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F134">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G134">
         <f t="shared" si="26"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H134">
         <f t="shared" si="27"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="I134">
         <f t="shared" si="28"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J134">
         <f t="shared" si="29"/>
-        <v>0.63888888888888884</v>
+        <v>1.2777777777777777</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -10130,14 +10137,14 @@
       </c>
       <c r="T134">
         <f t="shared" si="30"/>
-        <v>5.9156378600823052</v>
+        <v>11.83127572016461</v>
       </c>
       <c r="U134">
         <f t="shared" si="31"/>
-        <v>5.9156378600823052</v>
-      </c>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.83127572016461</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135">
         <v>333</v>
       </c>
@@ -10145,33 +10152,33 @@
         <v>42.5</v>
       </c>
       <c r="C135">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D135">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E135">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F135">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G135">
         <f t="shared" si="26"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="H135">
         <f t="shared" si="27"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I135">
         <f t="shared" si="28"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J135">
         <f t="shared" si="29"/>
-        <v>0.67647058823529416</v>
+        <v>1.3529411764705883</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -10202,14 +10209,14 @@
       </c>
       <c r="T135">
         <f t="shared" si="30"/>
-        <v>6.2636165577342053</v>
+        <v>12.527233115468411</v>
       </c>
       <c r="U135">
         <f t="shared" si="31"/>
-        <v>6.2636165577342053</v>
-      </c>
-    </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.527233115468411</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136">
         <v>333</v>
       </c>
@@ -10217,33 +10224,33 @@
         <v>40</v>
       </c>
       <c r="C136">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D136">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E136">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F136">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G136">
         <f t="shared" si="26"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="H136">
         <f t="shared" si="27"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="I136">
         <f t="shared" si="28"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="J136">
         <f t="shared" si="29"/>
-        <v>0.71875</v>
+        <v>1.4375</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -10274,14 +10281,14 @@
       </c>
       <c r="T136">
         <f t="shared" si="30"/>
-        <v>6.6550925925925934</v>
+        <v>13.310185185185187</v>
       </c>
       <c r="U136">
         <f t="shared" si="31"/>
-        <v>6.6550925925925934</v>
-      </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.310185185185187</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137">
         <v>333</v>
       </c>
@@ -10289,33 +10296,33 @@
         <v>37.5</v>
       </c>
       <c r="C137">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D137">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E137">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F137">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G137">
         <f t="shared" si="26"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H137">
         <f t="shared" si="27"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="I137">
         <f t="shared" si="28"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J137">
         <f t="shared" si="29"/>
-        <v>0.76666666666666661</v>
+        <v>1.5333333333333332</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -10346,14 +10353,14 @@
       </c>
       <c r="T137">
         <f t="shared" si="30"/>
-        <v>7.0987654320987659</v>
+        <v>14.197530864197532</v>
       </c>
       <c r="U137">
         <f t="shared" si="31"/>
-        <v>7.0987654320987659</v>
-      </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.197530864197532</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138">
         <v>333</v>
       </c>
@@ -10361,33 +10368,33 @@
         <v>35</v>
       </c>
       <c r="C138">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D138">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E138">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F138">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G138">
         <f t="shared" si="26"/>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="H138">
         <f t="shared" si="27"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="I138">
         <f t="shared" si="28"/>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="J138">
         <f t="shared" si="29"/>
-        <v>0.8214285714285714</v>
+        <v>1.6428571428571428</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -10418,14 +10425,14 @@
       </c>
       <c r="T138">
         <f t="shared" si="30"/>
-        <v>7.605820105820106</v>
+        <v>15.211640211640212</v>
       </c>
       <c r="U138">
         <f t="shared" si="31"/>
-        <v>7.605820105820106</v>
-      </c>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.211640211640212</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139">
         <v>333</v>
       </c>
@@ -10433,33 +10440,33 @@
         <v>32.5</v>
       </c>
       <c r="C139">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D139">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E139">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F139">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G139">
         <f t="shared" si="26"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="H139">
         <f t="shared" si="27"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="I139">
         <f t="shared" si="28"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J139">
         <f t="shared" si="29"/>
-        <v>0.8846153846153848</v>
+        <v>1.7692307692307696</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -10490,14 +10497,14 @@
       </c>
       <c r="T139">
         <f t="shared" si="30"/>
-        <v>8.1908831908831914</v>
+        <v>16.381766381766383</v>
       </c>
       <c r="U139">
         <f t="shared" si="31"/>
-        <v>8.1908831908831914</v>
-      </c>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>16.381766381766383</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140">
         <v>333</v>
       </c>
@@ -10505,33 +10512,33 @@
         <v>30</v>
       </c>
       <c r="C140">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D140">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E140">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F140">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G140">
         <f t="shared" si="26"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="H140">
         <f t="shared" si="27"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I140">
         <f t="shared" si="28"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="J140">
         <f t="shared" si="29"/>
-        <v>0.95833333333333337</v>
+        <v>1.9166666666666667</v>
       </c>
       <c r="K140">
         <v>0</v>
@@ -10562,14 +10569,14 @@
       </c>
       <c r="T140">
         <f t="shared" si="30"/>
-        <v>8.8734567901234573</v>
+        <v>17.746913580246915</v>
       </c>
       <c r="U140">
         <f t="shared" si="31"/>
-        <v>8.8734567901234573</v>
-      </c>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>17.746913580246915</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141">
         <v>333</v>
       </c>
@@ -10577,33 +10584,33 @@
         <v>27.5</v>
       </c>
       <c r="C141">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D141">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E141">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F141">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G141">
         <f t="shared" si="26"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="H141">
         <f t="shared" si="27"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="I141">
         <f t="shared" si="28"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="J141">
         <f t="shared" si="29"/>
-        <v>1.0454545454545456</v>
+        <v>2.0909090909090913</v>
       </c>
       <c r="K141">
         <v>0</v>
@@ -10634,14 +10641,14 @@
       </c>
       <c r="T141">
         <f t="shared" si="30"/>
-        <v>9.6801346801346799</v>
+        <v>19.36026936026936</v>
       </c>
       <c r="U141">
         <f t="shared" si="31"/>
-        <v>9.6801346801346799</v>
-      </c>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>19.36026936026936</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142">
         <v>333</v>
       </c>
@@ -10649,33 +10656,33 @@
         <v>25</v>
       </c>
       <c r="C142">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D142">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E142">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F142">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G142">
         <f t="shared" si="26"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H142">
         <f t="shared" si="27"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I142">
         <f t="shared" si="28"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J142">
         <f t="shared" si="29"/>
-        <v>1.1499999999999999</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K142">
         <v>0</v>
@@ -10706,14 +10713,14 @@
       </c>
       <c r="T142">
         <f t="shared" si="30"/>
-        <v>10.648148148148149</v>
+        <v>21.296296296296298</v>
       </c>
       <c r="U142">
         <f t="shared" si="31"/>
-        <v>10.648148148148149</v>
-      </c>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>21.296296296296298</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143">
         <v>333</v>
       </c>
@@ -10721,33 +10728,33 @@
         <v>22.5</v>
       </c>
       <c r="C143">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D143">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E143">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F143">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G143">
         <f t="shared" si="26"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H143">
         <f t="shared" si="27"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I143">
         <f t="shared" si="28"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J143">
         <f t="shared" si="29"/>
-        <v>1.2777777777777777</v>
+        <v>2.5555555555555554</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -10778,14 +10785,14 @@
       </c>
       <c r="T143">
         <f t="shared" si="30"/>
-        <v>11.83127572016461</v>
+        <v>23.662551440329221</v>
       </c>
       <c r="U143">
         <f t="shared" si="31"/>
-        <v>11.83127572016461</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>23.662551440329221</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144">
         <v>333</v>
       </c>
@@ -10793,33 +10800,33 @@
         <v>20</v>
       </c>
       <c r="C144">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D144">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E144">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F144">
         <f t="shared" si="32"/>
-        <v>958.33333333333337</v>
+        <v>1916.6666666666667</v>
       </c>
       <c r="G144">
         <f t="shared" si="26"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="H144">
         <f t="shared" si="27"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I144">
         <f t="shared" si="28"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="J144">
         <f t="shared" si="29"/>
-        <v>1.4375</v>
+        <v>2.875</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -10850,14 +10857,14 @@
       </c>
       <c r="T144">
         <f t="shared" si="30"/>
-        <v>13.310185185185187</v>
+        <v>26.620370370370374</v>
       </c>
       <c r="U144">
         <f t="shared" si="31"/>
-        <v>13.310185185185187</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>26.620370370370374</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145">
         <v>334</v>
       </c>
@@ -10865,33 +10872,33 @@
         <v>50</v>
       </c>
       <c r="C145">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D145">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E145">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F145">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G145">
         <f t="shared" si="26"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="H145">
         <f t="shared" si="27"/>
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="I145">
         <f t="shared" si="28"/>
-        <v>0.22499999999999998</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="J145">
         <f t="shared" si="29"/>
-        <v>0.47499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -10922,14 +10929,14 @@
       </c>
       <c r="T145">
         <f t="shared" si="30"/>
-        <v>4.3981481481481488</v>
+        <v>8.7962962962962976</v>
       </c>
       <c r="U145">
         <f t="shared" si="31"/>
-        <v>4.3981481481481488</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>8.7962962962962976</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146">
         <v>334</v>
       </c>
@@ -10937,33 +10944,33 @@
         <v>47.5</v>
       </c>
       <c r="C146">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D146">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E146">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F146">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G146">
         <f t="shared" si="26"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="H146">
         <f t="shared" si="27"/>
-        <v>0.13157894736842107</v>
+        <v>0.26315789473684215</v>
       </c>
       <c r="I146">
         <f t="shared" si="28"/>
-        <v>0.23684210526315791</v>
+        <v>0.47368421052631582</v>
       </c>
       <c r="J146">
         <f t="shared" si="29"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -10994,14 +11001,14 @@
       </c>
       <c r="T146">
         <f t="shared" si="30"/>
-        <v>4.6296296296296298</v>
+        <v>9.2592592592592595</v>
       </c>
       <c r="U146">
         <f t="shared" si="31"/>
-        <v>4.6296296296296298</v>
-      </c>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.2592592592592595</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147">
         <v>334</v>
       </c>
@@ -11009,33 +11016,33 @@
         <v>45</v>
       </c>
       <c r="C147">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D147">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E147">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F147">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G147">
         <f t="shared" si="26"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="H147">
         <f t="shared" si="27"/>
-        <v>0.1388888888888889</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="I147">
         <f t="shared" si="28"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J147">
         <f t="shared" si="29"/>
-        <v>0.52777777777777779</v>
+        <v>1.0555555555555556</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -11066,14 +11073,14 @@
       </c>
       <c r="T147">
         <f t="shared" si="30"/>
-        <v>4.8868312757201648</v>
+        <v>9.7736625514403297</v>
       </c>
       <c r="U147">
         <f t="shared" si="31"/>
-        <v>4.8868312757201648</v>
-      </c>
-    </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>9.7736625514403297</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148">
         <v>334</v>
       </c>
@@ -11081,33 +11088,33 @@
         <v>42.5</v>
       </c>
       <c r="C148">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D148">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E148">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F148">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G148">
         <f t="shared" si="26"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="H148">
         <f t="shared" si="27"/>
-        <v>0.14705882352941177</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I148">
         <f t="shared" si="28"/>
-        <v>0.26470588235294118</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J148">
         <f t="shared" si="29"/>
-        <v>0.55882352941176472</v>
+        <v>1.1176470588235294</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -11138,14 +11145,14 @@
       </c>
       <c r="T148">
         <f t="shared" si="30"/>
-        <v>5.1742919389978219</v>
+        <v>10.348583877995644</v>
       </c>
       <c r="U148">
         <f t="shared" si="31"/>
-        <v>5.1742919389978219</v>
-      </c>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.348583877995644</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149">
         <v>334</v>
       </c>
@@ -11153,33 +11160,33 @@
         <v>40</v>
       </c>
       <c r="C149">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D149">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E149">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F149">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G149">
         <f t="shared" si="26"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="H149">
         <f t="shared" si="27"/>
-        <v>0.15625000000000003</v>
+        <v>0.31250000000000006</v>
       </c>
       <c r="I149">
         <f t="shared" si="28"/>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="J149">
         <f t="shared" si="29"/>
-        <v>0.59375</v>
+        <v>1.1875</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -11210,14 +11217,14 @@
       </c>
       <c r="T149">
         <f t="shared" si="30"/>
-        <v>5.4976851851851851</v>
+        <v>10.99537037037037</v>
       </c>
       <c r="U149">
         <f t="shared" si="31"/>
-        <v>5.4976851851851851</v>
-      </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>10.99537037037037</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150">
         <v>334</v>
       </c>
@@ -11225,33 +11232,33 @@
         <v>37.5</v>
       </c>
       <c r="C150">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D150">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E150">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F150">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G150">
         <f t="shared" si="26"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="H150">
         <f t="shared" si="27"/>
-        <v>0.16666666666666669</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="I150">
         <f t="shared" si="28"/>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J150">
         <f t="shared" si="29"/>
-        <v>0.6333333333333333</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -11282,14 +11289,14 @@
       </c>
       <c r="T150">
         <f t="shared" si="30"/>
-        <v>5.8641975308641978</v>
+        <v>11.728395061728396</v>
       </c>
       <c r="U150">
         <f t="shared" si="31"/>
-        <v>5.8641975308641978</v>
-      </c>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>11.728395061728396</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151">
         <v>334</v>
       </c>
@@ -11297,33 +11304,33 @@
         <v>35</v>
       </c>
       <c r="C151">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D151">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E151">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F151">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G151">
         <f t="shared" si="26"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="H151">
         <f t="shared" si="27"/>
-        <v>0.17857142857142858</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="I151">
         <f t="shared" si="28"/>
-        <v>0.3214285714285714</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="J151">
         <f t="shared" si="29"/>
-        <v>0.6785714285714286</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -11354,14 +11361,14 @@
       </c>
       <c r="T151">
         <f t="shared" si="30"/>
-        <v>6.2830687830687841</v>
+        <v>12.566137566137568</v>
       </c>
       <c r="U151">
         <f t="shared" si="31"/>
-        <v>6.2830687830687841</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>12.566137566137568</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152">
         <v>334</v>
       </c>
@@ -11369,33 +11376,33 @@
         <v>32.5</v>
       </c>
       <c r="C152">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D152">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E152">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F152">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G152">
         <f t="shared" si="26"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H152">
         <f t="shared" si="27"/>
-        <v>0.19230769230769232</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="I152">
         <f t="shared" si="28"/>
-        <v>0.3461538461538462</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J152">
         <f t="shared" si="29"/>
-        <v>0.73076923076923084</v>
+        <v>1.4615384615384617</v>
       </c>
       <c r="K152">
         <v>0</v>
@@ -11426,14 +11433,14 @@
       </c>
       <c r="T152">
         <f t="shared" si="30"/>
-        <v>6.7663817663817678</v>
+        <v>13.532763532763536</v>
       </c>
       <c r="U152">
         <f t="shared" si="31"/>
-        <v>6.7663817663817678</v>
-      </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>13.532763532763536</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153">
         <v>334</v>
       </c>
@@ -11441,33 +11448,33 @@
         <v>30</v>
       </c>
       <c r="C153">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D153">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E153">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F153">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G153">
         <f t="shared" si="26"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H153">
         <f t="shared" si="27"/>
-        <v>0.20833333333333334</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I153">
         <f t="shared" si="28"/>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="J153">
         <f t="shared" si="29"/>
-        <v>0.79166666666666674</v>
+        <v>1.5833333333333335</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -11498,14 +11505,14 @@
       </c>
       <c r="T153">
         <f t="shared" si="30"/>
-        <v>7.3302469135802486</v>
+        <v>14.660493827160497</v>
       </c>
       <c r="U153">
         <f t="shared" si="31"/>
-        <v>7.3302469135802486</v>
-      </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>14.660493827160497</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154">
         <v>334</v>
       </c>
@@ -11513,33 +11520,33 @@
         <v>27.5</v>
       </c>
       <c r="C154">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D154">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E154">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F154">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G154">
         <f t="shared" si="26"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="H154">
         <f t="shared" si="27"/>
-        <v>0.22727272727272729</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="I154">
         <f t="shared" si="28"/>
-        <v>0.40909090909090912</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="J154">
         <f t="shared" si="29"/>
-        <v>0.86363636363636376</v>
+        <v>1.7272727272727275</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -11570,14 +11577,14 @@
       </c>
       <c r="T154">
         <f t="shared" si="30"/>
-        <v>7.9966329966329965</v>
+        <v>15.993265993265993</v>
       </c>
       <c r="U154">
         <f t="shared" si="31"/>
-        <v>7.9966329966329965</v>
-      </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>15.993265993265993</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155">
         <v>334</v>
       </c>
@@ -11585,33 +11592,33 @@
         <v>25</v>
       </c>
       <c r="C155">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D155">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E155">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F155">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G155">
         <f t="shared" si="26"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H155">
         <f t="shared" si="27"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I155">
         <f t="shared" si="28"/>
-        <v>0.44999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J155">
         <f t="shared" si="29"/>
-        <v>0.95</v>
+        <v>1.9</v>
       </c>
       <c r="K155">
         <v>0</v>
@@ -11642,14 +11649,14 @@
       </c>
       <c r="T155">
         <f t="shared" si="30"/>
-        <v>8.7962962962962976</v>
+        <v>17.592592592592595</v>
       </c>
       <c r="U155">
         <f t="shared" si="31"/>
-        <v>8.7962962962962976</v>
-      </c>
-    </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>17.592592592592595</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156">
         <v>334</v>
       </c>
@@ -11657,33 +11664,33 @@
         <v>22.5</v>
       </c>
       <c r="C156">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D156">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E156">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F156">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G156">
         <f t="shared" si="26"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H156">
         <f t="shared" si="27"/>
-        <v>0.27777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I156">
         <f t="shared" si="28"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J156">
         <f t="shared" si="29"/>
-        <v>1.0555555555555556</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="K156">
         <v>0</v>
@@ -11714,14 +11721,14 @@
       </c>
       <c r="T156">
         <f t="shared" si="30"/>
-        <v>9.7736625514403297</v>
+        <v>19.547325102880659</v>
       </c>
       <c r="U156">
         <f t="shared" si="31"/>
-        <v>9.7736625514403297</v>
-      </c>
-    </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>19.547325102880659</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157">
         <v>334</v>
       </c>
@@ -11729,33 +11736,33 @@
         <v>20</v>
       </c>
       <c r="C157">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="D157">
-        <v>208.33333333333334</v>
+        <v>416.66666666666669</v>
       </c>
       <c r="E157">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F157">
         <f t="shared" si="32"/>
-        <v>791.66666666666674</v>
+        <v>1583.3333333333335</v>
       </c>
       <c r="G157">
         <f t="shared" si="26"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="H157">
         <f t="shared" si="27"/>
-        <v>0.31250000000000006</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="I157">
         <f t="shared" si="28"/>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="J157">
         <f t="shared" si="29"/>
-        <v>1.1875</v>
+        <v>2.375</v>
       </c>
       <c r="K157">
         <v>0</v>
@@ -11786,14 +11793,23 @@
       </c>
       <c r="T157">
         <f t="shared" si="30"/>
-        <v>10.99537037037037</v>
+        <v>21.99074074074074</v>
       </c>
       <c r="U157">
         <f t="shared" si="31"/>
-        <v>10.99537037037037</v>
+        <v>21.99074074074074</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A157" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="313"/>
+        <filter val="314"/>
+        <filter val="324"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
